--- a/output/bases_limpias/Grupo_10_INSPECCIONES/df_ugsc_seguimiento.xlsx
+++ b/output/bases_limpias/Grupo_10_INSPECCIONES/df_ugsc_seguimiento.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA331"/>
+  <dimension ref="A1:AC331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,6 +552,16 @@
           <t>ubigeo</t>
         </is>
       </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ugel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -669,6 +679,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -782,6 +802,16 @@
           <t>180301</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>DRE MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>UGEL ILO</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -899,6 +929,16 @@
           <t>010602</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>UGEL RODRÍGUEZ DE MENDOZA</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1012,6 +1052,16 @@
           <t>211101</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>UGEL SAN ROMÁN</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1125,6 +1175,16 @@
           <t>150505</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>UGEL 08 CAÑETE</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1228,6 +1288,16 @@
           <t>150510</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>UGEL 08 CAÑETE</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1353,6 +1423,16 @@
           <t>030601</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHEROS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1470,6 +1550,16 @@
           <t>110112</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>UGEL ICA</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,6 +1663,16 @@
           <t>150516</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>UGEL 08 CAÑETE</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1782,16 @@
           <t>090117</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAVELICA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1899,16 @@
           <t>100109</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1902,6 +2022,16 @@
           <t>120702</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>UGEL TARMA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2021,6 +2151,16 @@
           <t>180104</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>DRE MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL NIETO</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2136,6 +2276,16 @@
           <t>180101</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>DRE MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL NIETO</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2249,6 +2399,16 @@
           <t>190201</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>UGEL DANIEL ALCIDES CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2358,6 +2518,16 @@
           <t>220803</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2469,6 +2639,16 @@
           <t>230102</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2578,6 +2758,16 @@
           <t>230110</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2683,6 +2873,16 @@
           <t>190110</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2992,16 @@
           <t>060406</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2901,6 +3111,16 @@
           <t>220402</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>UGEL HUALLAGA</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3014,6 +3234,16 @@
           <t>090116</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAVELICA</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3131,6 +3361,16 @@
           <t>090103</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAVELICA</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3248,6 +3488,16 @@
           <t>060603</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3361,6 +3611,16 @@
           <t>060612</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3480,6 +3740,16 @@
           <t>080101</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3595,6 +3865,16 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>090117</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAVELICA</t>
         </is>
       </c>
     </row>
@@ -3692,6 +3972,8 @@
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3801,6 +4083,16 @@
           <t>140107</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3914,6 +4206,16 @@
           <t>120303</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>UGEL PICHANAKI</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4025,6 +4327,16 @@
           <t>110102</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>UGEL ICA</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4138,6 +4450,16 @@
           <t>130613</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4249,6 +4571,16 @@
           <t>200303</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>UGEL HUANCABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4358,6 +4690,16 @@
           <t>200109</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>UGEL LA UNIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4469,6 +4811,16 @@
           <t>200405</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4578,6 +4930,16 @@
           <t>100507</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>UGEL LEONCIO PRADO</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4691,6 +5053,16 @@
           <t>020611</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>UGEL CARHUÁZ</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4802,6 +5174,16 @@
           <t>120210</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>UGEL CONCEPCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4911,6 +5293,16 @@
           <t>200704</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>UGEL TALARA</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5024,6 +5416,16 @@
           <t>060805</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>UGEL JAN</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5143,6 +5545,16 @@
           <t>080801</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5252,6 +5664,16 @@
           <t>090724</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>UGEL SURCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5359,6 +5781,16 @@
           <t>021904</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>UGEL SIHUAS</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5470,6 +5902,16 @@
           <t>030505</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>UGEL COTABAMBAS</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5581,6 +6023,16 @@
           <t>030413</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>UGEL AYMARAES</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5692,6 +6144,16 @@
           <t>030306</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>UGEL ANTABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5809,6 +6271,16 @@
           <t>030415</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>UGEL AYMARAES</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5924,6 +6396,16 @@
           <t>040302</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>UGEL CARAVELI</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6039,6 +6521,16 @@
           <t>040107</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6152,6 +6644,16 @@
           <t>040124</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6263,6 +6765,16 @@
           <t>060807</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>UGEL JAN</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6374,6 +6886,16 @@
           <t>021902</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>UGEL SIHUAS</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6483,6 +7005,16 @@
           <t>021904</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>UGEL SIHUAS</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6598,6 +7130,16 @@
           <t>100404</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>UGEL HUACAYBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6717,6 +7259,16 @@
           <t>120303</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>UGEL PICHANAKI</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6830,6 +7382,16 @@
           <t>180102</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>DRE MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL NIETO</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6937,6 +7499,16 @@
           <t>200405</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7056,6 +7628,16 @@
           <t>200803</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7175,6 +7757,16 @@
           <t>200601</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7286,6 +7878,16 @@
           <t>210115</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>UGEL PUNO</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7403,6 +8005,16 @@
           <t>220102</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>UGEL MOYOBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7516,6 +8128,16 @@
           <t>010206</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>UGEL BAGUA</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7631,6 +8253,16 @@
           <t>030201</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>UGEL ANDAHUAYLAS</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7742,6 +8374,16 @@
           <t>040129</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7861,6 +8503,16 @@
           <t>040307</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>UGEL CARAVELI</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7974,6 +8626,16 @@
           <t>040503</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8083,6 +8745,16 @@
           <t>050619</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>UGEL LUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8196,6 +8868,16 @@
           <t>050202</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>UGEL CANGALLO</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8305,6 +8987,16 @@
           <t>060414</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8412,6 +9104,16 @@
           <t>020105</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>UGEL HUARAZ</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8525,6 +9227,16 @@
           <t>080703</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8636,6 +9348,16 @@
           <t>090714</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8745,6 +9467,16 @@
           <t>080705</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8862,6 +9594,16 @@
           <t>080705</t>
         </is>
       </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8979,6 +9721,16 @@
           <t>081208</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9098,6 +9850,16 @@
           <t>100507</t>
         </is>
       </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>UGEL LEONCIO PRADO</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9209,6 +9971,16 @@
           <t>100201</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>UGEL AMBO</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9320,6 +10092,16 @@
           <t>100307</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>UGEL DOS DE MAYO</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9433,6 +10215,16 @@
           <t>120133</t>
         </is>
       </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9550,6 +10342,16 @@
           <t>120608</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>UGEL RIO TAMBO</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9659,6 +10461,16 @@
           <t>130104</t>
         </is>
       </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>UGEL 02 - LA ESPERANZA</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9770,6 +10582,16 @@
           <t>140111</t>
         </is>
       </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9881,6 +10703,16 @@
           <t>190101</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9996,6 +10828,16 @@
           <t>190101</t>
         </is>
       </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>UGEL PASCO</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10115,6 +10957,16 @@
           <t>190201</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>UGEL DANIEL ALCIDES CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10226,6 +11078,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10337,6 +11199,16 @@
           <t>200306</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10450,6 +11322,16 @@
           <t>200306</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10565,6 +11447,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10674,6 +11566,16 @@
           <t>210608</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAN</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10787,6 +11689,16 @@
           <t>210701</t>
         </is>
       </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>UGEL LAMPA</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10896,6 +11808,16 @@
           <t>211001</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>UGEL SAN ANTONIO DE PUTINA</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11007,6 +11929,16 @@
           <t>220104</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>UGEL MOYOBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11122,6 +12054,16 @@
           <t>220202</t>
         </is>
       </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>UGEL BELLAVISTA</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11231,6 +12173,16 @@
           <t>100313</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>UGEL DOS DE MAYO</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11338,6 +12290,16 @@
           <t>130801</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>UGEL PATAZ</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11453,6 +12415,16 @@
           <t>140107</t>
         </is>
       </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11562,6 +12534,16 @@
           <t>040601</t>
         </is>
       </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>UGEL CONDESUYOS</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11667,6 +12649,16 @@
           <t>140111</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11778,6 +12770,16 @@
           <t>140118</t>
         </is>
       </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11885,6 +12887,16 @@
           <t>220603</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL CÁCERES</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11998,6 +13010,16 @@
           <t>220801</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12111,6 +13133,16 @@
           <t>100801</t>
         </is>
       </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12218,6 +13250,16 @@
           <t>100111</t>
         </is>
       </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12335,6 +13377,16 @@
           <t>180104</t>
         </is>
       </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>DRE MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL NIETO</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12448,6 +13500,16 @@
           <t>040205</t>
         </is>
       </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>UGEL CAMANÁ</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12567,6 +13629,16 @@
           <t>040205</t>
         </is>
       </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>UGEL CAMANÁ</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12678,6 +13750,16 @@
           <t>050114</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12791,6 +13873,16 @@
           <t>080406</t>
         </is>
       </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>UGEL CALCA</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12904,6 +13996,16 @@
           <t>100801</t>
         </is>
       </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13017,6 +14119,16 @@
           <t>050114</t>
         </is>
       </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13128,6 +14240,16 @@
           <t>050106</t>
         </is>
       </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13241,6 +14363,16 @@
           <t>131202</t>
         </is>
       </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>UGEL VIRÚ</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13350,6 +14482,16 @@
           <t>210201</t>
         </is>
       </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13463,6 +14605,16 @@
           <t>080301</t>
         </is>
       </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>UGEL ANTA</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13572,6 +14724,16 @@
           <t>050505</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13679,6 +14841,16 @@
           <t>030414</t>
         </is>
       </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>UGEL AYMARAES</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13790,6 +14962,16 @@
           <t>200115</t>
         </is>
       </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13903,6 +15085,16 @@
           <t>200803</t>
         </is>
       </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14012,6 +15204,16 @@
           <t>200501</t>
         </is>
       </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>UGEL PAITA</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14117,6 +15319,16 @@
           <t>101102</t>
         </is>
       </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>UGEL YAROWILCA</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14226,6 +15438,16 @@
           <t>120908</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>UGEL CHUPACA</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14335,6 +15557,16 @@
           <t>140112</t>
         </is>
       </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14444,6 +15676,16 @@
           <t>060801</t>
         </is>
       </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>UGEL JAN</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14561,6 +15803,16 @@
           <t>200302</t>
         </is>
       </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14670,6 +15922,16 @@
           <t>220403</t>
         </is>
       </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>UGEL HUALLAGA</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14779,6 +16041,16 @@
           <t>210809</t>
         </is>
       </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14888,6 +16160,16 @@
           <t>210809</t>
         </is>
       </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14997,6 +16279,16 @@
           <t>210808</t>
         </is>
       </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15106,6 +16398,16 @@
           <t>210808</t>
         </is>
       </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15219,6 +16521,16 @@
           <t>210406</t>
         </is>
       </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>UGEL CHUCUITO</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15328,6 +16640,16 @@
           <t>200803</t>
         </is>
       </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15437,6 +16759,16 @@
           <t>200803</t>
         </is>
       </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>UGEL SECHURA</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15548,6 +16880,16 @@
           <t>200405</t>
         </is>
       </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15655,6 +16997,16 @@
           <t>130105</t>
         </is>
       </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>UGEL 02 - LA ESPERANZA</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15764,6 +17116,16 @@
           <t>100804</t>
         </is>
       </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15871,6 +17233,16 @@
           <t>090103</t>
         </is>
       </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAVELICA</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15984,6 +17356,16 @@
           <t>080707</t>
         </is>
       </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16091,6 +17473,16 @@
           <t>080702</t>
         </is>
       </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16200,6 +17592,16 @@
           <t>081303</t>
         </is>
       </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>UGEL URUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16311,6 +17713,16 @@
           <t>080705</t>
         </is>
       </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>UGEL CANAS</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16418,6 +17830,16 @@
           <t>060903</t>
         </is>
       </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16525,6 +17947,16 @@
           <t>060103</t>
         </is>
       </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16636,6 +18068,16 @@
           <t>050506</t>
         </is>
       </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16745,6 +18187,16 @@
           <t>050503</t>
         </is>
       </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16852,6 +18304,16 @@
           <t>010101</t>
         </is>
       </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16959,6 +18421,16 @@
           <t>030603</t>
         </is>
       </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHEROS</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17068,6 +18540,16 @@
           <t>080701</t>
         </is>
       </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17175,6 +18657,16 @@
           <t>210201</t>
         </is>
       </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17284,6 +18776,16 @@
           <t>080701</t>
         </is>
       </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17387,6 +18889,16 @@
           <t>060505</t>
         </is>
       </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>UGEL CONTUMAZÁ</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17490,6 +19002,16 @@
           <t>170301</t>
         </is>
       </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>UGEL TAHUAMANU</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17599,6 +19121,16 @@
           <t>080701</t>
         </is>
       </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17704,6 +19236,16 @@
           <t>080607</t>
         </is>
       </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>UGEL CANCHIS</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17807,6 +19349,16 @@
           <t>081303</t>
         </is>
       </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>UGEL URUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17916,6 +19468,16 @@
           <t>200111</t>
         </is>
       </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18029,6 +19591,16 @@
           <t>220104</t>
         </is>
       </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>UGEL MOYOBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18140,6 +19712,16 @@
           <t>050402</t>
         </is>
       </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18249,6 +19831,16 @@
           <t>200210</t>
         </is>
       </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18356,6 +19948,16 @@
           <t>080505</t>
         </is>
       </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>UGEL CANCHIS</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18457,6 +20059,16 @@
           <t>100109</t>
         </is>
       </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18560,6 +20172,16 @@
           <t>100111</t>
         </is>
       </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18669,6 +20291,16 @@
           <t>080917</t>
         </is>
       </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>UGEL PICHARI-KIMBIRI</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18772,6 +20404,16 @@
           <t>100509</t>
         </is>
       </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>UGEL HUAMALÍES</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18873,6 +20515,16 @@
           <t>210404</t>
         </is>
       </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>UGEL CHUCUITO</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18986,6 +20638,16 @@
           <t>211101</t>
         </is>
       </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>UGEL SAN ROMÁN</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19089,6 +20751,16 @@
           <t>100101</t>
         </is>
       </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19194,6 +20866,16 @@
           <t>100701</t>
         </is>
       </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>UGEL MARAÑÓN</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19301,6 +20983,16 @@
           <t>120907</t>
         </is>
       </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>UGEL CHUPACA</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19404,6 +21096,16 @@
           <t>211105</t>
         </is>
       </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>UGEL SAN ROMÁN</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19513,6 +21215,16 @@
           <t>160202</t>
         </is>
       </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19626,6 +21338,16 @@
           <t>060415</t>
         </is>
       </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19729,6 +21451,16 @@
           <t>200401</t>
         </is>
       </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>UGEL CHULUCANAS</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19838,6 +21570,16 @@
           <t>090719</t>
         </is>
       </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>UGEL TAYACAJA</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19939,6 +21681,16 @@
           <t>080108</t>
         </is>
       </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20040,6 +21792,16 @@
           <t>060906</t>
         </is>
       </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20141,6 +21903,16 @@
           <t>220803</t>
         </is>
       </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20248,6 +22020,16 @@
           <t>061306</t>
         </is>
       </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>UGEL SANTA CRUZ</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20359,6 +22141,16 @@
           <t>220301</t>
         </is>
       </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>UGEL EL DORADO</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20470,6 +22262,16 @@
           <t>100801</t>
         </is>
       </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20583,6 +22385,16 @@
           <t>060401</t>
         </is>
       </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20690,6 +22502,16 @@
           <t>061305</t>
         </is>
       </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>UGEL SANTA CRUZ</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20805,6 +22627,16 @@
           <t>040103</t>
         </is>
       </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20912,6 +22744,16 @@
           <t>130104</t>
         </is>
       </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>UGEL 02 - LA ESPERANZA</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21023,6 +22865,16 @@
           <t>010702</t>
         </is>
       </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>UGEL UTCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21136,6 +22988,16 @@
           <t>010702</t>
         </is>
       </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>UGEL UTCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21251,6 +23113,16 @@
           <t>221001</t>
         </is>
       </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>UGEL TOCACHE</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21358,6 +23230,16 @@
           <t>050106</t>
         </is>
       </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21463,6 +23345,16 @@
           <t>081002</t>
         </is>
       </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>UGEL PARURO</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21570,6 +23462,16 @@
           <t>050507</t>
         </is>
       </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21675,6 +23577,16 @@
           <t>080705</t>
         </is>
       </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21784,6 +23696,16 @@
           <t>051005</t>
         </is>
       </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>UGEL VÍCTOR FAJARDO</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21891,6 +23813,16 @@
           <t>040128</t>
         </is>
       </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21998,6 +23930,16 @@
           <t>160202</t>
         </is>
       </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22105,6 +24047,16 @@
           <t>080407</t>
         </is>
       </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>UGEL CALCA</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22212,6 +24164,16 @@
           <t>100201</t>
         </is>
       </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>UGEL AMBO</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22323,6 +24285,16 @@
           <t>100704</t>
         </is>
       </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>UGEL MARAÑÓN</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22430,6 +24402,16 @@
           <t>100802</t>
         </is>
       </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>UGEL PACHITEA</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22537,6 +24519,16 @@
           <t>140112</t>
         </is>
       </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22644,6 +24636,16 @@
           <t>130105</t>
         </is>
       </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>UGEL 02 - LA ESPERANZA</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22751,6 +24753,16 @@
           <t>220505</t>
         </is>
       </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>UGEL LAMAS</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22862,6 +24874,16 @@
           <t>030702</t>
         </is>
       </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>UGEL GRAU</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22967,6 +24989,16 @@
           <t>140104</t>
         </is>
       </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -23074,6 +25106,16 @@
           <t>120302</t>
         </is>
       </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>UGEL CHANCHAMAYO</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23181,6 +25223,16 @@
           <t>050409</t>
         </is>
       </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23282,6 +25334,16 @@
           <t>051105</t>
         </is>
       </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>UGEL VILCASHUAMÁN</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23389,6 +25451,16 @@
           <t>090206</t>
         </is>
       </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>UGEL ACOBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23492,6 +25564,16 @@
           <t>080807</t>
         </is>
       </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23593,6 +25675,16 @@
           <t>080701</t>
         </is>
       </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -23696,6 +25788,16 @@
           <t>210709</t>
         </is>
       </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>UGEL LAMPA</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -23805,6 +25907,16 @@
           <t>050115</t>
         </is>
       </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23912,6 +26024,16 @@
           <t>060812</t>
         </is>
       </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>UGEL JAN</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24017,6 +26139,16 @@
           <t>061101</t>
         </is>
       </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>UGEL SAN MIGUEL</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24120,6 +26252,16 @@
           <t>060807</t>
         </is>
       </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>UGEL JAN</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24225,6 +26367,16 @@
           <t>061101</t>
         </is>
       </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>UGEL SAN MIGUEL</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24334,6 +26486,16 @@
           <t>020305</t>
         </is>
       </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>UGEL ANTONIO RAYMONDI</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -24439,6 +26601,16 @@
           <t>100502</t>
         </is>
       </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>UGEL HUAMALÍES</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -24544,6 +26716,16 @@
           <t>100207</t>
         </is>
       </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>UGEL AMBO</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -24657,6 +26839,16 @@
           <t>140205</t>
         </is>
       </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24766,6 +26958,16 @@
           <t>200201</t>
         </is>
       </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24869,6 +27071,16 @@
           <t>210108</t>
         </is>
       </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>UGEL PUNO</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24974,6 +27186,16 @@
           <t>210902</t>
         </is>
       </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>UGEL MOHO</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -25081,6 +27303,16 @@
           <t>210707</t>
         </is>
       </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>UGEL LAMPA</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -25184,6 +27416,16 @@
           <t>210301</t>
         </is>
       </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>UGEL CARABAYA</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25291,6 +27533,16 @@
           <t>080702</t>
         </is>
       </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -25402,6 +27654,16 @@
           <t>200208</t>
         </is>
       </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -25509,6 +27771,16 @@
           <t>131005</t>
         </is>
       </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>UGEL SANTIAGO DE CHUCO</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -25612,6 +27884,16 @@
           <t>080708</t>
         </is>
       </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -25713,6 +27995,16 @@
           <t>101005</t>
         </is>
       </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>UGEL LAURICOCHA</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25814,6 +28106,16 @@
           <t>100901</t>
         </is>
       </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>UGEL PUERTO INCA</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -25915,6 +28217,16 @@
           <t>100902</t>
         </is>
       </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>UGEL PUERTO INCA</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -26016,6 +28328,16 @@
           <t>210707</t>
         </is>
       </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>UGEL LAMPA</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -26117,6 +28439,16 @@
           <t>210308</t>
         </is>
       </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>UGEL CARABAYA</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -26218,6 +28550,16 @@
           <t>210308</t>
         </is>
       </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>UGEL CARABAYA</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -26323,6 +28665,16 @@
           <t>080407</t>
         </is>
       </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -26424,6 +28776,16 @@
           <t>120114</t>
         </is>
       </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAYO</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -26525,6 +28887,16 @@
           <t>080106</t>
         </is>
       </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>UGEL CUSCO</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -26626,6 +28998,16 @@
           <t>050501</t>
         </is>
       </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -26733,6 +29115,16 @@
           <t>051012</t>
         </is>
       </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -26834,6 +29226,16 @@
           <t>030506</t>
         </is>
       </c>
+      <c r="AB241" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>UGEL COTABAMBAS</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -26935,6 +29337,16 @@
           <t>030506</t>
         </is>
       </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>UGEL COTABAMBAS</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -27038,6 +29450,16 @@
           <t>040121</t>
         </is>
       </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>UGEL LA JOYA</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27141,6 +29563,16 @@
           <t>050801</t>
         </is>
       </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>UGEL PAUCAR DE SARASARA</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -27244,6 +29676,16 @@
           <t>131001</t>
         </is>
       </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>UGEL SANTIAGO DE CHUCO</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -27349,6 +29791,16 @@
           <t>140110</t>
         </is>
       </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>UGEL CHICLAYO</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -27454,6 +29906,16 @@
           <t>090302</t>
         </is>
       </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -27559,6 +30021,16 @@
           <t>211303</t>
         </is>
       </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>UGEL YUNGUYO</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -27664,6 +30136,16 @@
           <t>200205</t>
         </is>
       </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>UGEL AYABACA</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -27771,6 +30253,16 @@
           <t>060405</t>
         </is>
       </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -27874,6 +30366,16 @@
           <t>220509</t>
         </is>
       </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>UGEL LAMAS</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -27981,6 +30483,16 @@
           <t>040104</t>
         </is>
       </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA NORTE</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28082,6 +30594,16 @@
           <t>060904</t>
         </is>
       </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -28183,6 +30705,16 @@
           <t>010511</t>
         </is>
       </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>UGEL LUYA</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -28292,6 +30824,16 @@
           <t>060202</t>
         </is>
       </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>UGEL CAJABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -28399,6 +30941,16 @@
           <t>060603</t>
         </is>
       </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -28502,6 +31054,16 @@
           <t>110201</t>
         </is>
       </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>UGEL CHINCHA</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -28609,6 +31171,16 @@
           <t>110504</t>
         </is>
       </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>UGEL PISCO</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -28714,6 +31286,16 @@
           <t>110101</t>
         </is>
       </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>DRE ICA</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>UGEL ICA</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -28823,6 +31405,16 @@
           <t>021805</t>
         </is>
       </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>UGEL SANTA</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -28930,6 +31522,16 @@
           <t>170102</t>
         </is>
       </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>DRE MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOPATA</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -29043,6 +31645,16 @@
           <t>200107</t>
         </is>
       </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>UGEL PIURA</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -29154,6 +31766,16 @@
           <t>080501</t>
         </is>
       </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>UGEL CANAS</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -29265,6 +31887,16 @@
           <t>120402</t>
         </is>
       </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>UGEL JAUJA</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -29378,6 +32010,16 @@
           <t>200304</t>
         </is>
       </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>UGEL HUARMACA</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -29487,6 +32129,16 @@
           <t>100112</t>
         </is>
       </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -29600,6 +32252,16 @@
           <t>100102</t>
         </is>
       </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -29703,6 +32365,16 @@
           <t>160202</t>
         </is>
       </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -29806,6 +32478,16 @@
           <t>080403</t>
         </is>
       </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>UGEL CALCA</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -29913,6 +32595,16 @@
           <t>130304</t>
         </is>
       </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>UGEL BOLIVAR</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -30016,6 +32708,16 @@
           <t>090118</t>
         </is>
       </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAVELICA</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -30119,6 +32821,16 @@
           <t>180101</t>
         </is>
       </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>DRE MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>UGEL MARISCAL NIETO</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -30228,6 +32940,16 @@
           <t>230406</t>
         </is>
       </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>UGEL TARATA</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -30335,6 +33057,16 @@
           <t>200308</t>
         </is>
       </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>UGEL HUANCABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -30442,6 +33174,16 @@
           <t>060407</t>
         </is>
       </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -30549,6 +33291,16 @@
           <t>210806</t>
         </is>
       </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -30654,6 +33406,16 @@
           <t>100604</t>
         </is>
       </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>UGEL LEONCIO PRADO</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -30763,6 +33525,16 @@
           <t>130903</t>
         </is>
       </c>
+      <c r="AB278" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AC278" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -30868,6 +33640,16 @@
           <t>140304</t>
         </is>
       </c>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -30979,6 +33761,16 @@
           <t>060415</t>
         </is>
       </c>
+      <c r="AB280" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC280" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -31088,6 +33880,16 @@
           <t>160101</t>
         </is>
       </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>UGEL MAYNAS</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -31191,6 +33993,16 @@
           <t>090207</t>
         </is>
       </c>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AC282" t="inlineStr">
+        <is>
+          <t>UGEL ACOBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -31292,6 +34104,16 @@
           <t>210807</t>
         </is>
       </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -31393,6 +34215,16 @@
           <t>030305</t>
         </is>
       </c>
+      <c r="AB284" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AC284" t="inlineStr">
+        <is>
+          <t>UGEL GRAU</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -31496,6 +34328,16 @@
           <t>131003</t>
         </is>
       </c>
+      <c r="AB285" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AC285" t="inlineStr">
+        <is>
+          <t>UGEL SANTIAGO DE CHUCO</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -31599,6 +34441,16 @@
           <t>010101</t>
         </is>
       </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AC286" t="inlineStr">
+        <is>
+          <t>UGEL CHACHAPOYAS</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -31702,6 +34554,16 @@
           <t>090305</t>
         </is>
       </c>
+      <c r="AB287" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AC287" t="inlineStr">
+        <is>
+          <t>UGEL ANGARAES</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -31805,6 +34667,16 @@
           <t>130102</t>
         </is>
       </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>UGEL 01 - EL PORVENIR</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -31908,6 +34780,16 @@
           <t>080502</t>
         </is>
       </c>
+      <c r="AB289" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC289" t="inlineStr">
+        <is>
+          <t>UGEL CANCHIS</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -32011,6 +34893,16 @@
           <t>010307</t>
         </is>
       </c>
+      <c r="AB290" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="AC290" t="inlineStr">
+        <is>
+          <t>UGEL BONGARÁ</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -32112,6 +35004,16 @@
           <t>081009</t>
         </is>
       </c>
+      <c r="AB291" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC291" t="inlineStr">
+        <is>
+          <t>UGEL PARURO</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -32215,6 +35117,16 @@
           <t>130503</t>
         </is>
       </c>
+      <c r="AB292" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AC292" t="inlineStr">
+        <is>
+          <t>UGEL JULCÁN</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -32318,6 +35230,16 @@
           <t>210803</t>
         </is>
       </c>
+      <c r="AB293" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC293" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -32421,6 +35343,16 @@
           <t>100901</t>
         </is>
       </c>
+      <c r="AB294" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC294" t="inlineStr">
+        <is>
+          <t>UGEL PUERTO INCA</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -32524,6 +35456,16 @@
           <t>210204</t>
         </is>
       </c>
+      <c r="AB295" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC295" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -32627,6 +35569,16 @@
           <t>130503</t>
         </is>
       </c>
+      <c r="AB296" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AC296" t="inlineStr">
+        <is>
+          <t>UGEL JULCÁN</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -32730,6 +35682,16 @@
           <t>100109</t>
         </is>
       </c>
+      <c r="AB297" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC297" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -32833,6 +35795,16 @@
           <t>081302</t>
         </is>
       </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC298" t="inlineStr">
+        <is>
+          <t>UGEL URUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -32936,6 +35908,16 @@
           <t>160201</t>
         </is>
       </c>
+      <c r="AB299" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="AC299" t="inlineStr">
+        <is>
+          <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -33039,6 +36021,16 @@
           <t>100111</t>
         </is>
       </c>
+      <c r="AB300" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC300" t="inlineStr">
+        <is>
+          <t>UGEL HUÁNUCO</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -33142,6 +36134,16 @@
           <t>060901</t>
         </is>
       </c>
+      <c r="AB301" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC301" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -33245,6 +36247,16 @@
           <t>210301</t>
         </is>
       </c>
+      <c r="AB302" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC302" t="inlineStr">
+        <is>
+          <t>UGEL CARABAYA</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -33348,6 +36360,16 @@
           <t>040110</t>
         </is>
       </c>
+      <c r="AB303" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AC303" t="inlineStr">
+        <is>
+          <t>UGEL AREQUIPA SUR</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -33449,6 +36471,16 @@
           <t>210114</t>
         </is>
       </c>
+      <c r="AB304" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC304" t="inlineStr">
+        <is>
+          <t>UGEL PUNO</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -33550,6 +36582,16 @@
           <t>130901</t>
         </is>
       </c>
+      <c r="AB305" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="AC305" t="inlineStr">
+        <is>
+          <t>UGEL SÁNCHEZ CARRIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -33651,6 +36693,16 @@
           <t>080805</t>
         </is>
       </c>
+      <c r="AB306" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC306" t="inlineStr">
+        <is>
+          <t>UGEL ESPINAR</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -33752,6 +36804,16 @@
           <t>060419</t>
         </is>
       </c>
+      <c r="AB307" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC307" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -33853,6 +36915,16 @@
           <t>060809</t>
         </is>
       </c>
+      <c r="AB308" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC308" t="inlineStr">
+        <is>
+          <t>UGEL JAN</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -33954,6 +37026,16 @@
           <t>060802</t>
         </is>
       </c>
+      <c r="AB309" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC309" t="inlineStr">
+        <is>
+          <t>UGEL JAN</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -34055,6 +37137,16 @@
           <t>030302</t>
         </is>
       </c>
+      <c r="AB310" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AC310" t="inlineStr">
+        <is>
+          <t>UGEL ANTABAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -34156,6 +37248,16 @@
           <t>100301</t>
         </is>
       </c>
+      <c r="AB311" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC311" t="inlineStr">
+        <is>
+          <t>UGEL DOS DE MAYO</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -34257,6 +37359,16 @@
           <t>210405</t>
         </is>
       </c>
+      <c r="AB312" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC312" t="inlineStr">
+        <is>
+          <t>UGEL CHUCUITO</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -34358,6 +37470,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="AB313" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC313" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -34459,6 +37581,16 @@
           <t>081006</t>
         </is>
       </c>
+      <c r="AB314" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="AC314" t="inlineStr">
+        <is>
+          <t>UGEL PARURO</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -34560,6 +37692,16 @@
           <t>100205</t>
         </is>
       </c>
+      <c r="AB315" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC315" t="inlineStr">
+        <is>
+          <t>UGEL AMBO</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -34661,6 +37803,16 @@
           <t>101103</t>
         </is>
       </c>
+      <c r="AB316" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC316" t="inlineStr">
+        <is>
+          <t>UGEL YAROWILCA</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -34768,6 +37920,16 @@
           <t>140304</t>
         </is>
       </c>
+      <c r="AB317" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr">
+        <is>
+          <t>UGEL LAMBAYEQUE</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -34869,6 +38031,16 @@
           <t>090717</t>
         </is>
       </c>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="AC318" t="inlineStr">
+        <is>
+          <t>UGEL SURCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -34972,6 +38144,16 @@
       <c r="AA319" t="inlineStr">
         <is>
           <t>211105</t>
+        </is>
+      </c>
+      <c r="AB319" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC319" t="inlineStr">
+        <is>
+          <t>UGEL SAN ROMÁN</t>
         </is>
       </c>
     </row>
@@ -35057,6 +38239,8 @@
       <c r="Y320" t="inlineStr"/>
       <c r="Z320" t="inlineStr"/>
       <c r="AA320" t="inlineStr"/>
+      <c r="AB320" t="inlineStr"/>
+      <c r="AC320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -35162,6 +38346,16 @@
           <t>230104</t>
         </is>
       </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>DRE TACNA</t>
+        </is>
+      </c>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>UGEL TACNA</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -35267,6 +38461,16 @@
           <t>210805</t>
         </is>
       </c>
+      <c r="AB322" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC322" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -35372,6 +38576,16 @@
           <t>210805</t>
         </is>
       </c>
+      <c r="AB323" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -35479,6 +38693,16 @@
           <t>060805</t>
         </is>
       </c>
+      <c r="AB324" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AC324" t="inlineStr">
+        <is>
+          <t>UGEL JAN</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -35586,6 +38810,16 @@
           <t>120608</t>
         </is>
       </c>
+      <c r="AB325" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="AC325" t="inlineStr">
+        <is>
+          <t>UGEL RIO TAMBO</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -35695,6 +38929,16 @@
           <t>200410</t>
         </is>
       </c>
+      <c r="AB326" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC326" t="inlineStr">
+        <is>
+          <t>UGEL MORROPÓN</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -35798,6 +39042,16 @@
           <t>200114</t>
         </is>
       </c>
+      <c r="AB327" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="AC327" t="inlineStr">
+        <is>
+          <t>UGEL TAMBOGRANDE</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -35899,6 +39153,16 @@
           <t>100307</t>
         </is>
       </c>
+      <c r="AB328" t="inlineStr">
+        <is>
+          <t>DRE HUANUCO</t>
+        </is>
+      </c>
+      <c r="AC328" t="inlineStr">
+        <is>
+          <t>UGEL DOS DE MAYO</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -36002,6 +39266,16 @@
           <t>050408</t>
         </is>
       </c>
+      <c r="AB329" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AC329" t="inlineStr">
+        <is>
+          <t>UGEL HUANTA</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -36103,6 +39377,16 @@
       <c r="AA330" t="inlineStr">
         <is>
           <t>160801</t>
+        </is>
+      </c>
+      <c r="AB330" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="AC330" t="inlineStr">
+        <is>
+          <t>UGEL PUTUMAYO</t>
         </is>
       </c>
     </row>
@@ -36140,6 +39424,8 @@
       <c r="Y331" t="inlineStr"/>
       <c r="Z331" t="inlineStr"/>
       <c r="AA331" t="inlineStr"/>
+      <c r="AB331" t="inlineStr"/>
+      <c r="AC331" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/bases_limpias/Grupo_10_INSPECCIONES/df_ugsc_seguimiento.xlsx
+++ b/output/bases_limpias/Grupo_10_INSPECCIONES/df_ugsc_seguimiento.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC331"/>
+  <dimension ref="A1:AD331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,6 +562,11 @@
           <t>ugel</t>
         </is>
       </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -689,6 +694,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -812,6 +822,11 @@
           <t>UGEL ILO</t>
         </is>
       </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -939,6 +954,11 @@
           <t>UGEL RODRÍGUEZ DE MENDOZA</t>
         </is>
       </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1062,6 +1082,11 @@
           <t>UGEL SAN ROMÁN</t>
         </is>
       </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
           <t>UGEL 08 CAÑETE</t>
         </is>
       </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
           <t>UGEL 08 CAÑETE</t>
         </is>
       </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1433,6 +1468,11 @@
           <t>UGEL CHINCHEROS</t>
         </is>
       </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
           <t>UGEL ICA</t>
         </is>
       </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1673,6 +1718,11 @@
           <t>UGEL 08 CAÑETE</t>
         </is>
       </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
           <t>UGEL HUANCAVELICA</t>
         </is>
       </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1909,6 +1964,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2032,6 +2092,11 @@
           <t>UGEL TARMA</t>
         </is>
       </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2161,6 +2226,11 @@
           <t>UGEL MARISCAL NIETO</t>
         </is>
       </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2286,6 +2356,11 @@
           <t>UGEL MARISCAL NIETO</t>
         </is>
       </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2409,6 +2484,11 @@
           <t>UGEL DANIEL ALCIDES CARRIÓN</t>
         </is>
       </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2528,6 +2608,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2649,6 +2734,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2768,6 +2858,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2883,6 +2978,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3002,6 +3102,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3121,6 +3226,11 @@
           <t>UGEL HUALLAGA</t>
         </is>
       </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3244,6 +3354,11 @@
           <t>UGEL HUANCAVELICA</t>
         </is>
       </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3371,6 +3486,11 @@
           <t>UGEL HUANCAVELICA</t>
         </is>
       </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3498,6 +3618,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3621,6 +3746,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3750,6 +3880,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3877,6 +4012,11 @@
           <t>UGEL HUANCAVELICA</t>
         </is>
       </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3967,13 +4107,42 @@
           <t>113823</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>CHUCUITO</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>ZEPITA</t>
+        </is>
+      </c>
       <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>210407</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>UGEL CHUCUITO</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4093,6 +4262,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4216,6 +4390,11 @@
           <t>UGEL PICHANAKI</t>
         </is>
       </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4337,6 +4516,11 @@
           <t>UGEL ICA</t>
         </is>
       </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4460,6 +4644,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4581,6 +4770,11 @@
           <t>UGEL HUANCABAMBA</t>
         </is>
       </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4700,6 +4894,11 @@
           <t>UGEL LA UNIÓN</t>
         </is>
       </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4821,6 +5020,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4940,6 +5144,11 @@
           <t>UGEL LEONCIO PRADO</t>
         </is>
       </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5063,6 +5272,11 @@
           <t>UGEL CARHUÁZ</t>
         </is>
       </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5184,6 +5398,11 @@
           <t>UGEL CONCEPCIÓN</t>
         </is>
       </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5303,6 +5522,11 @@
           <t>UGEL TALARA</t>
         </is>
       </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5426,6 +5650,11 @@
           <t>UGEL JAN</t>
         </is>
       </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5555,6 +5784,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5674,6 +5908,11 @@
           <t>UGEL SURCUBAMBA</t>
         </is>
       </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5791,6 +6030,11 @@
           <t>UGEL SIHUAS</t>
         </is>
       </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5912,6 +6156,11 @@
           <t>UGEL COTABAMBAS</t>
         </is>
       </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6033,6 +6282,11 @@
           <t>UGEL AYMARAES</t>
         </is>
       </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6154,6 +6408,11 @@
           <t>UGEL ANTABAMBA</t>
         </is>
       </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6281,6 +6540,11 @@
           <t>UGEL AYMARAES</t>
         </is>
       </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6406,6 +6670,11 @@
           <t>UGEL CARAVELI</t>
         </is>
       </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6531,6 +6800,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6654,6 +6928,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6775,6 +7054,11 @@
           <t>UGEL JAN</t>
         </is>
       </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6896,6 +7180,11 @@
           <t>UGEL SIHUAS</t>
         </is>
       </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7015,6 +7304,11 @@
           <t>UGEL SIHUAS</t>
         </is>
       </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7140,6 +7434,11 @@
           <t>UGEL HUACAYBAMBA</t>
         </is>
       </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7269,6 +7568,11 @@
           <t>UGEL PICHANAKI</t>
         </is>
       </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7392,6 +7696,11 @@
           <t>UGEL MARISCAL NIETO</t>
         </is>
       </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7509,6 +7818,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7638,6 +7952,11 @@
           <t>UGEL SECHURA</t>
         </is>
       </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7767,6 +8086,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7888,6 +8212,11 @@
           <t>UGEL PUNO</t>
         </is>
       </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8015,6 +8344,11 @@
           <t>UGEL MOYOBAMBA</t>
         </is>
       </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8138,6 +8472,11 @@
           <t>UGEL BAGUA</t>
         </is>
       </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8263,6 +8602,11 @@
           <t>UGEL ANDAHUAYLAS</t>
         </is>
       </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8384,6 +8728,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8513,6 +8862,11 @@
           <t>UGEL CARAVELI</t>
         </is>
       </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8636,6 +8990,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8755,6 +9114,11 @@
           <t>UGEL LUCANAS</t>
         </is>
       </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8878,6 +9242,11 @@
           <t>UGEL CANGALLO</t>
         </is>
       </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8997,6 +9366,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9114,6 +9488,11 @@
           <t>UGEL HUARAZ</t>
         </is>
       </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9237,6 +9616,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9358,6 +9742,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9477,6 +9866,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9604,6 +9998,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9731,6 +10130,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9860,6 +10264,11 @@
           <t>UGEL LEONCIO PRADO</t>
         </is>
       </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9981,6 +10390,11 @@
           <t>UGEL AMBO</t>
         </is>
       </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10102,6 +10516,11 @@
           <t>UGEL DOS DE MAYO</t>
         </is>
       </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10225,6 +10644,11 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10352,6 +10776,11 @@
           <t>UGEL RIO TAMBO</t>
         </is>
       </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10471,6 +10900,11 @@
           <t>UGEL 02 - LA ESPERANZA</t>
         </is>
       </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10592,6 +11026,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10713,6 +11152,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10838,6 +11282,11 @@
           <t>UGEL PASCO</t>
         </is>
       </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10967,6 +11416,11 @@
           <t>UGEL DANIEL ALCIDES CARRIÓN</t>
         </is>
       </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11088,6 +11542,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11209,6 +11668,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11332,6 +11796,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11457,6 +11926,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11576,6 +12050,11 @@
           <t>UGEL HUANCAN</t>
         </is>
       </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11699,6 +12178,11 @@
           <t>UGEL LAMPA</t>
         </is>
       </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11818,6 +12302,11 @@
           <t>UGEL SAN ANTONIO DE PUTINA</t>
         </is>
       </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11939,6 +12428,11 @@
           <t>UGEL MOYOBAMBA</t>
         </is>
       </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -12064,6 +12558,11 @@
           <t>UGEL BELLAVISTA</t>
         </is>
       </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -12183,6 +12682,11 @@
           <t>UGEL DOS DE MAYO</t>
         </is>
       </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -12300,6 +12804,11 @@
           <t>UGEL PATAZ</t>
         </is>
       </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12425,6 +12934,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12544,6 +13058,11 @@
           <t>UGEL CONDESUYOS</t>
         </is>
       </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12659,6 +13178,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12780,6 +13304,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12897,6 +13426,11 @@
           <t>UGEL MARISCAL CÁCERES</t>
         </is>
       </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -13020,6 +13554,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -13143,6 +13682,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -13260,6 +13804,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -13387,6 +13936,11 @@
           <t>UGEL MARISCAL NIETO</t>
         </is>
       </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13510,6 +14064,11 @@
           <t>UGEL CAMANÁ</t>
         </is>
       </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13639,6 +14198,11 @@
           <t>UGEL CAMANÁ</t>
         </is>
       </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13760,6 +14324,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13883,6 +14452,11 @@
           <t>UGEL CALCA</t>
         </is>
       </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -14006,6 +14580,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -14129,6 +14708,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -14250,6 +14834,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -14373,6 +14962,11 @@
           <t>UGEL VIRÚ</t>
         </is>
       </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -14492,6 +15086,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -14615,6 +15214,11 @@
           <t>UGEL ANTA</t>
         </is>
       </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14734,6 +15338,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14851,6 +15460,11 @@
           <t>UGEL AYMARAES</t>
         </is>
       </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14972,6 +15586,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -15095,6 +15714,11 @@
           <t>UGEL SECHURA</t>
         </is>
       </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -15214,6 +15838,11 @@
           <t>UGEL PAITA</t>
         </is>
       </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -15329,6 +15958,11 @@
           <t>UGEL YAROWILCA</t>
         </is>
       </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -15448,6 +16082,11 @@
           <t>UGEL CHUPACA</t>
         </is>
       </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -15567,6 +16206,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -15686,6 +16330,11 @@
           <t>UGEL JAN</t>
         </is>
       </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15813,6 +16462,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15932,6 +16586,11 @@
           <t>UGEL HUALLAGA</t>
         </is>
       </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -16051,6 +16710,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -16170,6 +16834,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -16289,6 +16958,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -16408,6 +17082,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -16531,6 +17210,11 @@
           <t>UGEL CHUCUITO</t>
         </is>
       </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -16650,6 +17334,11 @@
           <t>UGEL SECHURA</t>
         </is>
       </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -16769,6 +17458,11 @@
           <t>UGEL SECHURA</t>
         </is>
       </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -16890,6 +17584,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -17007,6 +17706,11 @@
           <t>UGEL 02 - LA ESPERANZA</t>
         </is>
       </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -17126,6 +17830,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -17243,6 +17952,11 @@
           <t>UGEL HUANCAVELICA</t>
         </is>
       </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -17366,6 +18080,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -17483,6 +18202,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -17602,6 +18326,11 @@
           <t>UGEL URUBAMBA</t>
         </is>
       </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -17723,6 +18452,11 @@
           <t>UGEL CANAS</t>
         </is>
       </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -17840,6 +18574,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -17957,6 +18696,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -18078,6 +18822,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -18197,6 +18946,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -18314,6 +19068,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -18431,6 +19190,11 @@
           <t>UGEL CHINCHEROS</t>
         </is>
       </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -18550,6 +19314,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -18667,6 +19436,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -18786,6 +19560,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -18899,6 +19678,11 @@
           <t>UGEL CONTUMAZÁ</t>
         </is>
       </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -19012,6 +19796,11 @@
           <t>UGEL TAHUAMANU</t>
         </is>
       </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -19131,6 +19920,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -19246,6 +20040,11 @@
           <t>UGEL CANCHIS</t>
         </is>
       </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -19359,6 +20158,11 @@
           <t>UGEL URUBAMBA</t>
         </is>
       </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -19478,6 +20282,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -19601,6 +20410,11 @@
           <t>UGEL MOYOBAMBA</t>
         </is>
       </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -19722,6 +20536,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -19841,6 +20660,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -19958,6 +20782,11 @@
           <t>UGEL CANCHIS</t>
         </is>
       </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -20069,6 +20898,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -20182,6 +21016,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -20301,6 +21140,11 @@
           <t>UGEL PICHARI-KIMBIRI</t>
         </is>
       </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -20414,6 +21258,11 @@
           <t>UGEL HUAMALÍES</t>
         </is>
       </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -20525,6 +21374,11 @@
           <t>UGEL CHUCUITO</t>
         </is>
       </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -20648,6 +21502,11 @@
           <t>UGEL SAN ROMÁN</t>
         </is>
       </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -20761,6 +21620,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -20876,6 +21740,11 @@
           <t>UGEL MARAÑÓN</t>
         </is>
       </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -20993,6 +21862,11 @@
           <t>UGEL CHUPACA</t>
         </is>
       </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -21106,6 +21980,11 @@
           <t>UGEL SAN ROMÁN</t>
         </is>
       </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -21225,6 +22104,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -21348,6 +22232,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -21461,6 +22350,11 @@
           <t>UGEL CHULUCANAS</t>
         </is>
       </c>
+      <c r="AD174" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -21580,6 +22474,11 @@
           <t>UGEL TAYACAJA</t>
         </is>
       </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -21691,6 +22590,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -21802,6 +22706,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -21913,6 +22822,11 @@
           <t>UGEL RIOJA</t>
         </is>
       </c>
+      <c r="AD178" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -22030,6 +22944,11 @@
           <t>UGEL SANTA CRUZ</t>
         </is>
       </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -22151,6 +23070,11 @@
           <t>UGEL EL DORADO</t>
         </is>
       </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -22272,6 +23196,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AD181" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -22395,6 +23324,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -22512,6 +23446,11 @@
           <t>UGEL SANTA CRUZ</t>
         </is>
       </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -22637,6 +23576,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -22754,6 +23698,11 @@
           <t>UGEL 02 - LA ESPERANZA</t>
         </is>
       </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -22875,6 +23824,11 @@
           <t>UGEL UTCUBAMBA</t>
         </is>
       </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -22998,6 +23952,11 @@
           <t>UGEL UTCUBAMBA</t>
         </is>
       </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -23123,6 +24082,11 @@
           <t>UGEL TOCACHE</t>
         </is>
       </c>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -23240,6 +24204,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -23355,6 +24324,11 @@
           <t>UGEL PARURO</t>
         </is>
       </c>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -23472,6 +24446,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -23587,6 +24566,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -23706,6 +24690,11 @@
           <t>UGEL VÍCTOR FAJARDO</t>
         </is>
       </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -23823,6 +24812,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -23940,6 +24934,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -24057,6 +25056,11 @@
           <t>UGEL CALCA</t>
         </is>
       </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -24174,6 +25178,11 @@
           <t>UGEL AMBO</t>
         </is>
       </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -24295,6 +25304,11 @@
           <t>UGEL MARAÑÓN</t>
         </is>
       </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -24412,6 +25426,11 @@
           <t>UGEL PACHITEA</t>
         </is>
       </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -24529,6 +25548,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -24646,6 +25670,11 @@
           <t>UGEL 02 - LA ESPERANZA</t>
         </is>
       </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -24763,6 +25792,11 @@
           <t>UGEL LAMAS</t>
         </is>
       </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -24884,6 +25918,11 @@
           <t>UGEL GRAU</t>
         </is>
       </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -24999,6 +26038,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -25116,6 +26160,11 @@
           <t>UGEL CHANCHAMAYO</t>
         </is>
       </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -25233,6 +26282,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -25344,6 +26398,11 @@
           <t>UGEL VILCASHUAMÁN</t>
         </is>
       </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -25461,6 +26520,11 @@
           <t>UGEL ACOBAMBA</t>
         </is>
       </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -25574,6 +26638,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -25685,6 +26754,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -25798,6 +26872,11 @@
           <t>UGEL LAMPA</t>
         </is>
       </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -25917,6 +26996,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -26034,6 +27118,11 @@
           <t>UGEL JAN</t>
         </is>
       </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -26149,6 +27238,11 @@
           <t>UGEL SAN MIGUEL</t>
         </is>
       </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -26262,6 +27356,11 @@
           <t>UGEL JAN</t>
         </is>
       </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -26377,6 +27476,11 @@
           <t>UGEL SAN MIGUEL</t>
         </is>
       </c>
+      <c r="AD216" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -26496,6 +27600,11 @@
           <t>UGEL ANTONIO RAYMONDI</t>
         </is>
       </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -26611,6 +27720,11 @@
           <t>UGEL HUAMALÍES</t>
         </is>
       </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -26726,6 +27840,11 @@
           <t>UGEL AMBO</t>
         </is>
       </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -26849,6 +27968,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="AD220" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -26968,6 +28092,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -27081,6 +28210,11 @@
           <t>UGEL PUNO</t>
         </is>
       </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -27196,6 +28330,11 @@
           <t>UGEL MOHO</t>
         </is>
       </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -27313,6 +28452,11 @@
           <t>UGEL LAMPA</t>
         </is>
       </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -27426,6 +28570,11 @@
           <t>UGEL CARABAYA</t>
         </is>
       </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -27543,6 +28692,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -27664,6 +28818,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -27781,6 +28940,11 @@
           <t>UGEL SANTIAGO DE CHUCO</t>
         </is>
       </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -27894,6 +29058,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -28005,6 +29174,11 @@
           <t>UGEL LAURICOCHA</t>
         </is>
       </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -28116,6 +29290,11 @@
           <t>UGEL PUERTO INCA</t>
         </is>
       </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -28227,6 +29406,11 @@
           <t>UGEL PUERTO INCA</t>
         </is>
       </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -28338,6 +29522,11 @@
           <t>UGEL LAMPA</t>
         </is>
       </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -28449,6 +29638,11 @@
           <t>UGEL CARABAYA</t>
         </is>
       </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -28560,6 +29754,11 @@
           <t>UGEL CARABAYA</t>
         </is>
       </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -28675,6 +29874,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -28786,6 +29990,11 @@
           <t>UGEL HUANCAYO</t>
         </is>
       </c>
+      <c r="AD237" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -28897,6 +30106,11 @@
           <t>UGEL CUSCO</t>
         </is>
       </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -29008,6 +30222,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -29125,6 +30344,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="AD240" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -29236,6 +30460,11 @@
           <t>UGEL COTABAMBAS</t>
         </is>
       </c>
+      <c r="AD241" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -29347,6 +30576,11 @@
           <t>UGEL COTABAMBAS</t>
         </is>
       </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -29460,6 +30694,11 @@
           <t>UGEL LA JOYA</t>
         </is>
       </c>
+      <c r="AD243" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -29573,6 +30812,11 @@
           <t>UGEL PAUCAR DE SARASARA</t>
         </is>
       </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -29686,6 +30930,11 @@
           <t>UGEL SANTIAGO DE CHUCO</t>
         </is>
       </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -29801,6 +31050,11 @@
           <t>UGEL CHICLAYO</t>
         </is>
       </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -29916,6 +31170,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -30031,6 +31290,11 @@
           <t>UGEL YUNGUYO</t>
         </is>
       </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -30146,6 +31410,11 @@
           <t>UGEL AYABACA</t>
         </is>
       </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -30263,6 +31532,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -30376,6 +31650,11 @@
           <t>UGEL LAMAS</t>
         </is>
       </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -30493,6 +31772,11 @@
           <t>UGEL AREQUIPA NORTE</t>
         </is>
       </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -30604,6 +31888,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -30715,6 +32004,11 @@
           <t>UGEL LUYA</t>
         </is>
       </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -30834,6 +32128,11 @@
           <t>UGEL CAJABAMBA</t>
         </is>
       </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -30951,6 +32250,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -31064,6 +32368,11 @@
           <t>UGEL CHINCHA</t>
         </is>
       </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -31181,6 +32490,11 @@
           <t>UGEL PISCO</t>
         </is>
       </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -31296,6 +32610,11 @@
           <t>UGEL ICA</t>
         </is>
       </c>
+      <c r="AD259" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -31415,6 +32734,11 @@
           <t>UGEL SANTA</t>
         </is>
       </c>
+      <c r="AD260" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -31532,6 +32856,11 @@
           <t>UGEL TAMBOPATA</t>
         </is>
       </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -31655,6 +32984,11 @@
           <t>UGEL PIURA</t>
         </is>
       </c>
+      <c r="AD262" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -31776,6 +33110,11 @@
           <t>UGEL CANAS</t>
         </is>
       </c>
+      <c r="AD263" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -31897,6 +33236,11 @@
           <t>UGEL JAUJA</t>
         </is>
       </c>
+      <c r="AD264" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -32020,6 +33364,11 @@
           <t>UGEL HUARMACA</t>
         </is>
       </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -32139,6 +33488,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="AD266" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -32262,6 +33616,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="AD267" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -32375,6 +33734,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="AD268" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -32488,6 +33852,11 @@
           <t>UGEL CALCA</t>
         </is>
       </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -32605,6 +33974,11 @@
           <t>UGEL BOLIVAR</t>
         </is>
       </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -32718,6 +34092,11 @@
           <t>UGEL HUANCAVELICA</t>
         </is>
       </c>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -32831,6 +34210,11 @@
           <t>UGEL MARISCAL NIETO</t>
         </is>
       </c>
+      <c r="AD272" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -32950,6 +34334,11 @@
           <t>UGEL TARATA</t>
         </is>
       </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -33067,6 +34456,11 @@
           <t>UGEL HUANCABAMBA</t>
         </is>
       </c>
+      <c r="AD274" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -33184,6 +34578,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="AD275" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -33301,6 +34700,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="AD276" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -33416,6 +34820,11 @@
           <t>UGEL LEONCIO PRADO</t>
         </is>
       </c>
+      <c r="AD277" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -33535,6 +34944,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="AD278" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -33650,6 +35064,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="AD279" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -33771,6 +35190,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="AD280" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -33890,6 +35314,11 @@
           <t>UGEL MAYNAS</t>
         </is>
       </c>
+      <c r="AD281" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -34003,6 +35432,11 @@
           <t>UGEL ACOBAMBA</t>
         </is>
       </c>
+      <c r="AD282" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -34114,6 +35548,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="AD283" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -34225,6 +35664,11 @@
           <t>UGEL GRAU</t>
         </is>
       </c>
+      <c r="AD284" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -34338,6 +35782,11 @@
           <t>UGEL SANTIAGO DE CHUCO</t>
         </is>
       </c>
+      <c r="AD285" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -34451,6 +35900,11 @@
           <t>UGEL CHACHAPOYAS</t>
         </is>
       </c>
+      <c r="AD286" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -34564,6 +36018,11 @@
           <t>UGEL ANGARAES</t>
         </is>
       </c>
+      <c r="AD287" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -34677,6 +36136,11 @@
           <t>UGEL 01 - EL PORVENIR</t>
         </is>
       </c>
+      <c r="AD288" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -34790,6 +36254,11 @@
           <t>UGEL CANCHIS</t>
         </is>
       </c>
+      <c r="AD289" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -34903,6 +36372,11 @@
           <t>UGEL BONGARÁ</t>
         </is>
       </c>
+      <c r="AD290" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -35014,6 +36488,11 @@
           <t>UGEL PARURO</t>
         </is>
       </c>
+      <c r="AD291" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -35127,6 +36606,11 @@
           <t>UGEL JULCÁN</t>
         </is>
       </c>
+      <c r="AD292" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -35240,6 +36724,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="AD293" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -35353,6 +36842,11 @@
           <t>UGEL PUERTO INCA</t>
         </is>
       </c>
+      <c r="AD294" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -35466,6 +36960,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="AD295" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -35579,6 +37078,11 @@
           <t>UGEL JULCÁN</t>
         </is>
       </c>
+      <c r="AD296" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -35692,6 +37196,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="AD297" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -35805,6 +37314,11 @@
           <t>UGEL URUBAMBA</t>
         </is>
       </c>
+      <c r="AD298" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -35918,6 +37432,11 @@
           <t>UGEL ALTO AMAZONAS-YURIMAGUAS</t>
         </is>
       </c>
+      <c r="AD299" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -36031,6 +37550,11 @@
           <t>UGEL HUÁNUCO</t>
         </is>
       </c>
+      <c r="AD300" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -36144,6 +37668,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="AD301" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -36257,6 +37786,11 @@
           <t>UGEL CARABAYA</t>
         </is>
       </c>
+      <c r="AD302" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -36370,6 +37904,11 @@
           <t>UGEL AREQUIPA SUR</t>
         </is>
       </c>
+      <c r="AD303" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -36481,6 +38020,11 @@
           <t>UGEL PUNO</t>
         </is>
       </c>
+      <c r="AD304" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -36592,6 +38136,11 @@
           <t>UGEL SÁNCHEZ CARRIÓN</t>
         </is>
       </c>
+      <c r="AD305" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -36703,6 +38252,11 @@
           <t>UGEL ESPINAR</t>
         </is>
       </c>
+      <c r="AD306" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -36814,6 +38368,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="AD307" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -36925,6 +38484,11 @@
           <t>UGEL JAN</t>
         </is>
       </c>
+      <c r="AD308" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -37036,6 +38600,11 @@
           <t>UGEL JAN</t>
         </is>
       </c>
+      <c r="AD309" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -37147,6 +38716,11 @@
           <t>UGEL ANTABAMBA</t>
         </is>
       </c>
+      <c r="AD310" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -37258,6 +38832,11 @@
           <t>UGEL DOS DE MAYO</t>
         </is>
       </c>
+      <c r="AD311" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -37369,6 +38948,11 @@
           <t>UGEL CHUCUITO</t>
         </is>
       </c>
+      <c r="AD312" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -37480,6 +39064,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="AD313" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -37591,6 +39180,11 @@
           <t>UGEL PARURO</t>
         </is>
       </c>
+      <c r="AD314" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -37702,6 +39296,11 @@
           <t>UGEL AMBO</t>
         </is>
       </c>
+      <c r="AD315" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -37813,6 +39412,11 @@
           <t>UGEL YAROWILCA</t>
         </is>
       </c>
+      <c r="AD316" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -37930,6 +39534,11 @@
           <t>UGEL LAMBAYEQUE</t>
         </is>
       </c>
+      <c r="AD317" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -38041,6 +39650,11 @@
           <t>UGEL SURCUBAMBA</t>
         </is>
       </c>
+      <c r="AD318" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -38156,6 +39770,11 @@
           <t>UGEL SAN ROMÁN</t>
         </is>
       </c>
+      <c r="AD319" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -38234,13 +39853,42 @@
           <t>918034</t>
         </is>
       </c>
-      <c r="W320" t="inlineStr"/>
-      <c r="X320" t="inlineStr"/>
-      <c r="Y320" t="inlineStr"/>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>MOHO</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>TILALI</t>
+        </is>
+      </c>
       <c r="Z320" t="inlineStr"/>
-      <c r="AA320" t="inlineStr"/>
-      <c r="AB320" t="inlineStr"/>
-      <c r="AC320" t="inlineStr"/>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>210904</t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="AC320" t="inlineStr">
+        <is>
+          <t>UGEL MOHO</t>
+        </is>
+      </c>
+      <c r="AD320" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -38356,6 +40004,11 @@
           <t>UGEL TACNA</t>
         </is>
       </c>
+      <c r="AD321" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -38471,6 +40124,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="AD322" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -38586,6 +40244,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="AD323" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -38703,6 +40366,11 @@
           <t>UGEL JAN</t>
         </is>
       </c>
+      <c r="AD324" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -38820,6 +40488,11 @@
           <t>UGEL RIO TAMBO</t>
         </is>
       </c>
+      <c r="AD325" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -38939,6 +40612,11 @@
           <t>UGEL MORROPÓN</t>
         </is>
       </c>
+      <c r="AD326" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -39052,6 +40730,11 @@
           <t>UGEL TAMBOGRANDE</t>
         </is>
       </c>
+      <c r="AD327" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -39163,6 +40846,11 @@
           <t>UGEL DOS DE MAYO</t>
         </is>
       </c>
+      <c r="AD328" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -39276,6 +40964,11 @@
           <t>UGEL HUANTA</t>
         </is>
       </c>
+      <c r="AD329" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -39387,6 +41080,11 @@
       <c r="AC330" t="inlineStr">
         <is>
           <t>UGEL PUTUMAYO</t>
+        </is>
+      </c>
+      <c r="AD330" t="inlineStr">
+        <is>
+          <t>UGSC</t>
         </is>
       </c>
     </row>
@@ -39426,6 +41124,11 @@
       <c r="AA331" t="inlineStr"/>
       <c r="AB331" t="inlineStr"/>
       <c r="AC331" t="inlineStr"/>
+      <c r="AD331" t="inlineStr">
+        <is>
+          <t>UGSC</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/bases_limpias/Grupo_10_INSPECCIONES/df_ugsc_seguimiento.xlsx
+++ b/output/bases_limpias/Grupo_10_INSPECCIONES/df_ugsc_seguimiento.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD331"/>
+  <dimension ref="A1:AF331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,6 +564,16 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
           <t>fuente</t>
         </is>
       </c>
@@ -696,6 +706,16 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -824,6 +844,16 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
+          <t>ALMTE. MIGUEL GRAU SEMINARIO/ALMTE. MIGUEL GRAU SEMINARIO/ALMTE. MIGUEL GRAU SEMINARIO</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -956,6 +986,16 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1084,6 +1124,16 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
+          <t>RODOLFO DIESEL</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1212,6 +1262,16 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
+          <t>NUESTRA SEÑORA DE LA ASUNCION/NUESTRA SEÑORA DE LA ASUNCION</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1330,6 +1390,16 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
+          <t>AUGUSTO B. LEGUIA/AUGUSTO B. LEGUIA</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1470,6 +1540,16 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
+          <t>CHINCHEROS</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1602,6 +1682,16 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1720,6 +1810,16 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
+          <t>NUESTRA SEÑORA DE LA ASUNCION</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1844,6 +1944,16 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -1966,6 +2076,16 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
+          <t>32706/32706</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2094,6 +2214,16 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
+          <t>EXALTACION DE LA SANTA CRUZ/EXALTACION DE LA SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2228,6 +2358,16 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2358,6 +2498,16 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
+          <t>PRITE ANDREE RENATO SANCHEZ SOTO</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2486,6 +2636,16 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
+          <t>MANUEL GONZALES PRADA</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2610,6 +2770,16 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
+          <t>00623/00623</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2736,6 +2906,16 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
+          <t>GUILLERMO AUZA ARCE/GUILLERMO AUZA ARCE/GUILLERMO AUZA ARCE</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2860,6 +3040,16 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
+          <t>LUIS ALBERTO SANCHEZ/LUIS ALBERTO SANCHEZ/LUIS ALBERTO SANCHEZ/LUIS ALBERTO SANCHEZ/LUIS ALBERTO SANCHEZ</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -2980,6 +3170,16 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
+          <t>DEMETRIO TEMPLADERA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -3104,6 +3304,16 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
+          <t>SAN FRANCISCO</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -3228,6 +3438,12 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
+          <t>0600 AUGUSTO SALAZAR BONDY</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -3356,6 +3572,16 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
+          <t>36059</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -3488,6 +3714,16 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -3620,6 +3856,16 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
+          <t>JOSE CARLOS MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -3748,6 +3994,16 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
+          <t>JOSE SOTERO LOZANO</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -3882,6 +4138,16 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4014,6 +4280,16 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4140,6 +4416,16 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
+          <t>TUCAHUI</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4264,6 +4550,16 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
+          <t>SAN FRANCISCO</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4392,6 +4688,16 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
+          <t>NUEVA ESPERANZA/NUEVA ESPERANZA/NUEVA ESPERANZA</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4518,6 +4824,16 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
+          <t>22491 MICAELA BASTIDAS PUYUCAWA/22491 MICAELA BASTIDAS PUYUCAWA</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4646,6 +4962,16 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
+          <t>80700 CARLOS NORIEGA JIMENEZ/80700 CARLOS NORIEGA JIMENEZ</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4772,6 +5098,16 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
+          <t>14456 DANIEL ALCIDES CARRION/14456 DANIEL ALCIDES CARRION/14456 DANIEL ALCIDES CARRION</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -4896,6 +5232,16 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
+          <t>14121/14121/14121/14121</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5022,6 +5368,16 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
+          <t>14652</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5146,6 +5502,16 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
+          <t>TAZO GRANDE/TAZO GRANDE/TAZO GRANDE</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5274,6 +5640,16 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
+          <t>86283 SAN MARTIN DE PORRAS/86283 SAN MARTIN DE PORRAS</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5400,6 +5776,16 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
+          <t>AGROPECUARIO 111</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5524,6 +5910,16 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
+          <t>602 SANTA ROSA DE LIMA</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5652,6 +6048,16 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
+          <t>16562</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5786,6 +6192,16 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
+          <t>CORONEL LADISLAO ESPINAR/CORONEL LADISLAO ESPINAR/CORONEL LADISLAO ESPINAR/CORONEL LADISLAO ESPINAR</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -5910,6 +6326,16 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
+          <t>31108</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6032,6 +6458,16 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
+          <t>84188 ANGEL VICTOR PONTE ARCE</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6158,6 +6594,16 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
+          <t>50673</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6284,6 +6730,16 @@
       </c>
       <c r="AD46" t="inlineStr">
         <is>
+          <t>54323 SAN ANTONIO DE PADUA</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6410,6 +6866,16 @@
       </c>
       <c r="AD47" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6542,6 +7008,16 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
+          <t>FRANCISCO BOLOGNESI CERVANTES</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6672,6 +7148,16 @@
       </c>
       <c r="AD49" t="inlineStr">
         <is>
+          <t>40262 JOSE SEBASTIAN BARRANCA Y LOVERA</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6802,6 +7288,16 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
+          <t>40033 SAN AGUSTIN DE HUNTER/40033 SAN AGUSTIN DE HUNTER</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -6930,6 +7426,16 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
+          <t>40092 JOSE D. ZUZUNAGA OBANDO/40092 JOSE D. ZUZUNAGA OBANDO</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7056,6 +7562,16 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
+          <t>16967</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7182,6 +7698,16 @@
       </c>
       <c r="AD53" t="inlineStr">
         <is>
+          <t>84173</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7306,6 +7832,16 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7436,6 +7972,16 @@
       </c>
       <c r="AD55" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7570,6 +8116,16 @@
       </c>
       <c r="AD56" t="inlineStr">
         <is>
+          <t>LOS ANGELES/LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7698,6 +8254,16 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
+          <t>43044</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7820,6 +8386,16 @@
       </c>
       <c r="AD58" t="inlineStr">
         <is>
+          <t>FELIPE COSSIO DEL POMAR/FELIPE COSSIO DEL POMAR/ALMIRANTE MIGUEL GRAU</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -7954,6 +8530,16 @@
       </c>
       <c r="AD59" t="inlineStr">
         <is>
+          <t>BERNAL/BERNAL/BERNAL</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8088,6 +8674,16 @@
       </c>
       <c r="AD60" t="inlineStr">
         <is>
+          <t>15085 JAVIER PEREZ DE CUELLAR/15085 JAVIER PEREZ DE CUELLAR</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8214,6 +8810,16 @@
       </c>
       <c r="AD61" t="inlineStr">
         <is>
+          <t>70040</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8346,6 +8952,16 @@
       </c>
       <c r="AD62" t="inlineStr">
         <is>
+          <t>00743 BLANCA ROSA ANDUAGA DE CARO</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8474,6 +9090,16 @@
       </c>
       <c r="AD63" t="inlineStr">
         <is>
+          <t>16195</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8604,6 +9230,16 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
+          <t>277-43 VIRGEN DE CANDELARIA/54118</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8730,6 +9366,16 @@
       </c>
       <c r="AD65" t="inlineStr">
         <is>
+          <t>40175 GRAN LIBERTADOR SIMON BOLIVAR/40175 GRAN LIBERTADOR SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8864,6 +9510,16 @@
       </c>
       <c r="AD66" t="inlineStr">
         <is>
+          <t>40272 JOSE OLAYA BALANDRA</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -8992,6 +9648,16 @@
       </c>
       <c r="AD67" t="inlineStr">
         <is>
+          <t>CABANACONDE</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -9116,6 +9782,16 @@
       </c>
       <c r="AD68" t="inlineStr">
         <is>
+          <t>JOSE MARIA ARGUEDAS</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -9244,6 +9920,16 @@
       </c>
       <c r="AD69" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -9368,6 +10054,16 @@
       </c>
       <c r="AD70" t="inlineStr">
         <is>
+          <t>JOSE MANUEL OSORES</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -9490,6 +10186,16 @@
       </c>
       <c r="AD71" t="inlineStr">
         <is>
+          <t>PEDRO TAHUA AMBROCIO</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -9618,6 +10324,16 @@
       </c>
       <c r="AD72" t="inlineStr">
         <is>
+          <t>56263 SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -9744,6 +10460,16 @@
       </c>
       <c r="AD73" t="inlineStr">
         <is>
+          <t>CESAR VALLEJO</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -9868,6 +10594,16 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
+          <t>56370 MARIO VARGAS LLOSA/56370 MARIO VARGAS LLOSA/56370 MARIO VARGAS LLOSA</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10000,6 +10736,16 @@
       </c>
       <c r="AD75" t="inlineStr">
         <is>
+          <t>JOSE MARIA ARGUEDAS/56381/56381</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10132,6 +10878,16 @@
       </c>
       <c r="AD76" t="inlineStr">
         <is>
+          <t>50480</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10266,6 +11022,16 @@
       </c>
       <c r="AD77" t="inlineStr">
         <is>
+          <t>32888</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10392,6 +11158,16 @@
       </c>
       <c r="AD78" t="inlineStr">
         <is>
+          <t>PRITE RAYITOS DE ESPERANZA/33083/33083</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10518,6 +11294,16 @@
       </c>
       <c r="AD79" t="inlineStr">
         <is>
+          <t>33398</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10646,6 +11432,16 @@
       </c>
       <c r="AD80" t="inlineStr">
         <is>
+          <t>30026</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10778,6 +11574,16 @@
       </c>
       <c r="AD81" t="inlineStr">
         <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -10902,6 +11708,16 @@
       </c>
       <c r="AD82" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11028,6 +11844,16 @@
       </c>
       <c r="AD83" t="inlineStr">
         <is>
+          <t>080 TESORITOS DE MARIA</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11154,6 +11980,16 @@
       </c>
       <c r="AD84" t="inlineStr">
         <is>
+          <t>35001 CIPRIANO PROAÑO/35001 CIPRIANO PROAÑO</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11284,6 +12120,16 @@
       </c>
       <c r="AD85" t="inlineStr">
         <is>
+          <t>34003 TUPAC AMARU/34003</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11418,6 +12264,16 @@
       </c>
       <c r="AD86" t="inlineStr">
         <is>
+          <t>PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11544,6 +12400,16 @@
       </c>
       <c r="AD87" t="inlineStr">
         <is>
+          <t>CARLOS AUGUSTO SALAVERRY/CARLOS AUGUSTO SALAVERRY/CARLOS AUGUSTO SALAVERRY</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11670,6 +12536,16 @@
       </c>
       <c r="AD88" t="inlineStr">
         <is>
+          <t>14514 MARIO VARGAS LLOSA/14514 MARIO VARGAS LLOSA/14514 MARIO VARGAS LLOSA</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11798,6 +12674,16 @@
       </c>
       <c r="AD89" t="inlineStr">
         <is>
+          <t>RODRIGO CHINCHAY PACHECO/RODRIGO CHINCHAY PACHECO/RODRIGO CHINCHAY PACHECO</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -11928,6 +12814,16 @@
       </c>
       <c r="AD90" t="inlineStr">
         <is>
+          <t>MANUEL ASCENCIO SEGURA/MANUEL ASCENCIO SEGURA/MANUEL ASCENCIO SEGURA</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12052,6 +12948,16 @@
       </c>
       <c r="AD91" t="inlineStr">
         <is>
+          <t>SICTA</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12180,6 +13086,16 @@
       </c>
       <c r="AD92" t="inlineStr">
         <is>
+          <t>71010</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12304,6 +13220,16 @@
       </c>
       <c r="AD93" t="inlineStr">
         <is>
+          <t>72126 GLORIOSO SANTIAGO GIRALDO</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12430,6 +13356,16 @@
       </c>
       <c r="AD94" t="inlineStr">
         <is>
+          <t>00514 MONSEÑOR VENANCIO CELESTINO ORBE URIARTE/00514 MONSEÑOR VENANCIO CELESTINO ORBE URIARTE</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12560,6 +13496,16 @@
       </c>
       <c r="AD95" t="inlineStr">
         <is>
+          <t>0489 JORGE CHAVEZ DARNELL/0489 JORGE CHAVEZ DARNELL</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12684,6 +13630,16 @@
       </c>
       <c r="AD96" t="inlineStr">
         <is>
+          <t>024</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12806,6 +13762,16 @@
       </c>
       <c r="AD97" t="inlineStr">
         <is>
+          <t>80424 ANTONIO RAYMONDI/80424 ANTONIO RAYMONDI</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -12936,6 +13902,16 @@
       </c>
       <c r="AD98" t="inlineStr">
         <is>
+          <t>11185/11185</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13060,6 +14036,16 @@
       </c>
       <c r="AD99" t="inlineStr">
         <is>
+          <t>SAN LUIS GONZAGA</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13180,6 +14166,16 @@
       </c>
       <c r="AD100" t="inlineStr">
         <is>
+          <t>11134/11134</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13306,6 +14302,16 @@
       </c>
       <c r="AD101" t="inlineStr">
         <is>
+          <t>OCTAVIO CAMPOS OTOLEAS/OCTAVIO CAMPOS OTOLEAS/OCTAVIO CAMPOS OTOLEAS/OCTAVIO CAMPOS OTOLEAS</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13428,6 +14434,16 @@
       </c>
       <c r="AD102" t="inlineStr">
         <is>
+          <t>0420</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13556,6 +14572,16 @@
       </c>
       <c r="AD103" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13684,6 +14710,16 @@
       </c>
       <c r="AD104" t="inlineStr">
         <is>
+          <t>32600/32600/32600</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13806,6 +14842,16 @@
       </c>
       <c r="AD105" t="inlineStr">
         <is>
+          <t>32271/32271</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -13938,6 +14984,16 @@
       </c>
       <c r="AD106" t="inlineStr">
         <is>
+          <t>43016 VITALIANO BECERRA HERRERA</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14066,6 +15122,16 @@
       </c>
       <c r="AD107" t="inlineStr">
         <is>
+          <t>SAN GREGORIO</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14200,6 +15266,16 @@
       </c>
       <c r="AD108" t="inlineStr">
         <is>
+          <t>40239 NICOLAS DE PIEROLA/40239 NICOLAS DE PIEROLA</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14326,6 +15402,16 @@
       </c>
       <c r="AD109" t="inlineStr">
         <is>
+          <t>38575</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14454,6 +15540,16 @@
       </c>
       <c r="AD110" t="inlineStr">
         <is>
+          <t>50741</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14582,6 +15678,16 @@
       </c>
       <c r="AD111" t="inlineStr">
         <is>
+          <t>33438</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14710,6 +15816,16 @@
       </c>
       <c r="AD112" t="inlineStr">
         <is>
+          <t>38103</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14836,6 +15952,16 @@
       </c>
       <c r="AD113" t="inlineStr">
         <is>
+          <t>HERMES ANYOSA SALVATIERRA</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -14964,6 +16090,16 @@
       </c>
       <c r="AD114" t="inlineStr">
         <is>
+          <t>82206 VALLE DE DIOS/82206 VALLE DE DIOS</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15088,6 +16224,16 @@
       </c>
       <c r="AD115" t="inlineStr">
         <is>
+          <t>SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15216,6 +16362,16 @@
       </c>
       <c r="AD116" t="inlineStr">
         <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15340,6 +16496,16 @@
       </c>
       <c r="AD117" t="inlineStr">
         <is>
+          <t>VILLA AURORA</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15462,6 +16628,16 @@
       </c>
       <c r="AD118" t="inlineStr">
         <is>
+          <t>54325 VIRGEN DE NATIVIDAD</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15588,6 +16764,16 @@
       </c>
       <c r="AD119" t="inlineStr">
         <is>
+          <t>14008 LEONOR CERNA DE VALDIVIEZO/14008 LEONOR CERNA DE VALDIVIEZO/14008 LEONOR CERNA DE VALDIVIEZO</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15716,6 +16902,16 @@
       </c>
       <c r="AD120" t="inlineStr">
         <is>
+          <t>14028</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15840,6 +17036,16 @@
       </c>
       <c r="AD121" t="inlineStr">
         <is>
+          <t>14741 SEÑOR DE LOS MILAGROS/14741 SEÑOR DE LOS MILAGROS/14741 SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -15960,6 +17166,16 @@
       </c>
       <c r="AD122" t="inlineStr">
         <is>
+          <t>CESAR VALLEJO MENDOZA</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16084,6 +17300,16 @@
       </c>
       <c r="AD123" t="inlineStr">
         <is>
+          <t>SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16208,6 +17434,16 @@
       </c>
       <c r="AD124" t="inlineStr">
         <is>
+          <t>10005 SANTA ROSA DE LIMA</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16332,6 +17568,16 @@
       </c>
       <c r="AD125" t="inlineStr">
         <is>
+          <t>16042 FRANCISCO BOLOGNESI/16042 FRANCISCO BOLOGNESI</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16464,6 +17710,16 @@
       </c>
       <c r="AD126" t="inlineStr">
         <is>
+          <t>14502</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16588,6 +17844,16 @@
       </c>
       <c r="AD127" t="inlineStr">
         <is>
+          <t>0751 JAIME H. ROJAS CHAVEZ</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16712,6 +17978,16 @@
       </c>
       <c r="AD128" t="inlineStr">
         <is>
+          <t>70498</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16836,6 +18112,16 @@
       </c>
       <c r="AD129" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -16960,6 +18246,16 @@
       </c>
       <c r="AD130" t="inlineStr">
         <is>
+          <t>70475 SAN JUAN BAUTISTA DE LA SALLE</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17084,6 +18380,16 @@
       </c>
       <c r="AD131" t="inlineStr">
         <is>
+          <t>LA SALLE</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17212,6 +18518,16 @@
       </c>
       <c r="AD132" t="inlineStr">
         <is>
+          <t>LLAQUEPA</t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17336,6 +18652,16 @@
       </c>
       <c r="AD133" t="inlineStr">
         <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17460,6 +18786,16 @@
       </c>
       <c r="AD134" t="inlineStr">
         <is>
+          <t>14024/14024</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17586,6 +18922,16 @@
       </c>
       <c r="AD135" t="inlineStr">
         <is>
+          <t>ANTONIO RAYMONDI/ANTONIO RAYMONDI</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17708,6 +19054,16 @@
       </c>
       <c r="AD136" t="inlineStr">
         <is>
+          <t>2307</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17832,6 +19188,16 @@
       </c>
       <c r="AD137" t="inlineStr">
         <is>
+          <t>32629/32629</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -17954,6 +19320,16 @@
       </c>
       <c r="AD138" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18082,6 +19458,16 @@
       </c>
       <c r="AD139" t="inlineStr">
         <is>
+          <t>JOSE ANTONIO ENCINAS</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18204,6 +19590,16 @@
       </c>
       <c r="AD140" t="inlineStr">
         <is>
+          <t>LAS AMERICAS</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18328,6 +19724,16 @@
       </c>
       <c r="AD141" t="inlineStr">
         <is>
+          <t>50589</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18454,6 +19860,16 @@
       </c>
       <c r="AD142" t="inlineStr">
         <is>
+          <t>56268 FERNANDO BELAUNDE TERRY/56268 FERNANDO BELAUNDE TERRY</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18576,6 +19992,16 @@
       </c>
       <c r="AD143" t="inlineStr">
         <is>
+          <t>16501 JUAN ALBACETE SAIZ/16501 JUAN ALBACETE SAIZ</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18698,6 +20124,16 @@
       </c>
       <c r="AD144" t="inlineStr">
         <is>
+          <t>821502</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18824,6 +20260,16 @@
       </c>
       <c r="AD145" t="inlineStr">
         <is>
+          <t>38430</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -18948,6 +20394,16 @@
       </c>
       <c r="AD146" t="inlineStr">
         <is>
+          <t>SAN FRANCISCO/WALTER PEÑALOZA RAMELLA/39017/SAN FRANCISCO</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19070,6 +20526,16 @@
       </c>
       <c r="AD147" t="inlineStr">
         <is>
+          <t>403 CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19192,6 +20658,16 @@
       </c>
       <c r="AD148" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19316,6 +20792,16 @@
       </c>
       <c r="AD149" t="inlineStr">
         <is>
+          <t>501377 JOSE CARLOS MARIATEGUI/501377 JOSE CARLOS MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19438,6 +20924,16 @@
       </c>
       <c r="AD150" t="inlineStr">
         <is>
+          <t>72724</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19562,6 +21058,16 @@
       </c>
       <c r="AD151" t="inlineStr">
         <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19680,6 +21186,16 @@
       </c>
       <c r="AD152" t="inlineStr">
         <is>
+          <t>1455</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19798,6 +21314,16 @@
       </c>
       <c r="AD153" t="inlineStr">
         <is>
+          <t>52144</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -19922,6 +21448,16 @@
       </c>
       <c r="AD154" t="inlineStr">
         <is>
+          <t>56354/56354</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20042,6 +21578,16 @@
       </c>
       <c r="AD155" t="inlineStr">
         <is>
+          <t>56037</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20160,6 +21706,16 @@
       </c>
       <c r="AD156" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20284,6 +21840,16 @@
       </c>
       <c r="AD157" t="inlineStr">
         <is>
+          <t>SANTA ROSA DE LIMA</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20412,6 +21978,16 @@
       </c>
       <c r="AD158" t="inlineStr">
         <is>
+          <t>WILFREDO ZEGARRA SANDOVAL</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20538,6 +22114,16 @@
       </c>
       <c r="AD159" t="inlineStr">
         <is>
+          <t>JULIO RAMON RIBEYRO ZUÑIGA</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20662,6 +22248,16 @@
       </c>
       <c r="AD160" t="inlineStr">
         <is>
+          <t>14309</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20784,6 +22380,16 @@
       </c>
       <c r="AD161" t="inlineStr">
         <is>
+          <t>56134</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -20900,6 +22506,16 @@
       </c>
       <c r="AD162" t="inlineStr">
         <is>
+          <t>LLIHUARI/32728</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21018,6 +22634,16 @@
       </c>
       <c r="AD163" t="inlineStr">
         <is>
+          <t>231 MI PEQUEÑO MUNDO</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21142,6 +22768,16 @@
       </c>
       <c r="AD164" t="inlineStr">
         <is>
+          <t>38896</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21260,6 +22896,16 @@
       </c>
       <c r="AD165" t="inlineStr">
         <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21376,6 +23022,16 @@
       </c>
       <c r="AD166" t="inlineStr">
         <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21504,6 +23160,16 @@
       </c>
       <c r="AD167" t="inlineStr">
         <is>
+          <t>SANTA MONICA</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21622,6 +23288,16 @@
       </c>
       <c r="AD168" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21742,6 +23418,16 @@
       </c>
       <c r="AD169" t="inlineStr">
         <is>
+          <t>460/84318</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21864,6 +23550,16 @@
       </c>
       <c r="AD170" t="inlineStr">
         <is>
+          <t>LOS ANDES</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -21982,6 +23678,16 @@
       </c>
       <c r="AD171" t="inlineStr">
         <is>
+          <t>PERU BIRF/PERU BIRF</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22106,6 +23812,16 @@
       </c>
       <c r="AD172" t="inlineStr">
         <is>
+          <t>62432/62432</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22234,6 +23950,16 @@
       </c>
       <c r="AD173" t="inlineStr">
         <is>
+          <t>10589</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22352,6 +24078,16 @@
       </c>
       <c r="AD174" t="inlineStr">
         <is>
+          <t>DOS DE MAYO</t>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22476,6 +24212,16 @@
       </c>
       <c r="AD175" t="inlineStr">
         <is>
+          <t>JUAN VELASCO ALVARADO</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22592,6 +24338,16 @@
       </c>
       <c r="AD176" t="inlineStr">
         <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22708,6 +24464,16 @@
       </c>
       <c r="AD177" t="inlineStr">
         <is>
+          <t>16520 RICARDO PALMA/16520 RICARDO PALMA</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22824,6 +24590,16 @@
       </c>
       <c r="AD178" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -22946,6 +24722,16 @@
       </c>
       <c r="AD179" t="inlineStr">
         <is>
+          <t>CESAR A. VALLEJO MENDOZA</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23072,6 +24858,16 @@
       </c>
       <c r="AD180" t="inlineStr">
         <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23198,6 +24994,16 @@
       </c>
       <c r="AD181" t="inlineStr">
         <is>
+          <t>33340</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23326,6 +25132,16 @@
       </c>
       <c r="AD182" t="inlineStr">
         <is>
+          <t>10391</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23448,6 +25264,16 @@
       </c>
       <c r="AD183" t="inlineStr">
         <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23578,6 +25404,16 @@
       </c>
       <c r="AD184" t="inlineStr">
         <is>
+          <t>40654/40654</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23700,6 +25536,16 @@
       </c>
       <c r="AD185" t="inlineStr">
         <is>
+          <t>80081 JULIO GUTIERREZ SOLARI/80081 JULIO GUTIERREZ SOLARI</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23826,6 +25672,16 @@
       </c>
       <c r="AD186" t="inlineStr">
         <is>
+          <t>16783/16783</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -23954,6 +25810,16 @@
       </c>
       <c r="AD187" t="inlineStr">
         <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24084,6 +25950,16 @@
       </c>
       <c r="AD188" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24206,6 +26082,16 @@
       </c>
       <c r="AD189" t="inlineStr">
         <is>
+          <t>ANDRES AVELINO CACERES</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24326,6 +26212,16 @@
       </c>
       <c r="AD190" t="inlineStr">
         <is>
+          <t>50361/50361</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24448,6 +26344,16 @@
       </c>
       <c r="AD191" t="inlineStr">
         <is>
+          <t>38443</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24568,6 +26474,16 @@
       </c>
       <c r="AD192" t="inlineStr">
         <is>
+          <t>56289 RICARDO PALMA DE QQUECHAPAMPA/56289 RICARDO PALMA DE QQUECHAPAMPA</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24692,6 +26608,16 @@
       </c>
       <c r="AD193" t="inlineStr">
         <is>
+          <t>38464</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24814,6 +26740,16 @@
       </c>
       <c r="AD194" t="inlineStr">
         <is>
+          <t>ESTACION YURA</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -24936,6 +26872,16 @@
       </c>
       <c r="AD195" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25058,6 +27004,16 @@
       </c>
       <c r="AD196" t="inlineStr">
         <is>
+          <t>50185</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25180,6 +27136,16 @@
       </c>
       <c r="AD197" t="inlineStr">
         <is>
+          <t>32167 JOSE OLAYA BALANDRA/32167 JOSE OLAYA BALANDRA</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25306,6 +27272,16 @@
       </c>
       <c r="AD198" t="inlineStr">
         <is>
+          <t>32725</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25428,6 +27404,16 @@
       </c>
       <c r="AD199" t="inlineStr">
         <is>
+          <t>32584</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25550,6 +27536,16 @@
       </c>
       <c r="AD200" t="inlineStr">
         <is>
+          <t>10014 SAN MARTIN DE PORRES</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25672,6 +27668,16 @@
       </c>
       <c r="AD201" t="inlineStr">
         <is>
+          <t>2336</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25794,6 +27800,16 @@
       </c>
       <c r="AD202" t="inlineStr">
         <is>
+          <t>0282 MARIA HIDALGO TORRES</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -25920,6 +27936,16 @@
       </c>
       <c r="AD203" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26040,6 +28066,16 @@
       </c>
       <c r="AD204" t="inlineStr">
         <is>
+          <t>018 MELODIAS DEL MAR</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26162,6 +28198,16 @@
       </c>
       <c r="AD205" t="inlineStr">
         <is>
+          <t>PERENE/PERENE/PERENE/PERENE</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26284,6 +28330,16 @@
       </c>
       <c r="AD206" t="inlineStr">
         <is>
+          <t>38741</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26400,6 +28456,16 @@
       </c>
       <c r="AD207" t="inlineStr">
         <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26522,6 +28588,16 @@
       </c>
       <c r="AD208" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26640,6 +28716,16 @@
       </c>
       <c r="AD209" t="inlineStr">
         <is>
+          <t>56369</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26756,6 +28842,16 @@
       </c>
       <c r="AD210" t="inlineStr">
         <is>
+          <t>56319 ROSA DE SANTA MARIA/56319 ROSA DE SANTA MARIA</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26874,6 +28970,16 @@
       </c>
       <c r="AD211" t="inlineStr">
         <is>
+          <t>INDUSTRIAL SANTA LUCIA</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -26998,6 +29104,16 @@
       </c>
       <c r="AD212" t="inlineStr">
         <is>
+          <t>104 SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27120,6 +29236,16 @@
       </c>
       <c r="AD213" t="inlineStr">
         <is>
+          <t>16190/16190/16190</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27240,6 +29366,16 @@
       </c>
       <c r="AD214" t="inlineStr">
         <is>
+          <t>82854</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27358,6 +29494,16 @@
       </c>
       <c r="AD215" t="inlineStr">
         <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27478,6 +29624,16 @@
       </c>
       <c r="AD216" t="inlineStr">
         <is>
+          <t>82740</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27602,6 +29758,16 @@
       </c>
       <c r="AD217" t="inlineStr">
         <is>
+          <t>86231 MANUEL GONZALES PRADA</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27722,6 +29888,16 @@
       </c>
       <c r="AD218" t="inlineStr">
         <is>
+          <t>32395</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27842,6 +30018,16 @@
       </c>
       <c r="AD219" t="inlineStr">
         <is>
+          <t>33327</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -27970,6 +30156,16 @@
       </c>
       <c r="AD220" t="inlineStr">
         <is>
+          <t>11534 JOSE E. CAMPOS PERALTA</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28094,6 +30290,16 @@
       </c>
       <c r="AD221" t="inlineStr">
         <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28212,6 +30418,16 @@
       </c>
       <c r="AD222" t="inlineStr">
         <is>
+          <t>SAN JUAN DE HUATTA</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF222" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28332,6 +30548,16 @@
       </c>
       <c r="AD223" t="inlineStr">
         <is>
+          <t>72354</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28454,6 +30680,16 @@
       </c>
       <c r="AD224" t="inlineStr">
         <is>
+          <t>CHILAHUITO</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28572,6 +30808,16 @@
       </c>
       <c r="AD225" t="inlineStr">
         <is>
+          <t>POLITECNICO INDUSTRIAL MACUSANI</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28694,6 +30940,16 @@
       </c>
       <c r="AD226" t="inlineStr">
         <is>
+          <t>824/56262</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28820,6 +31076,16 @@
       </c>
       <c r="AD227" t="inlineStr">
         <is>
+          <t>14401/14401/14401</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -28942,6 +31208,16 @@
       </c>
       <c r="AD228" t="inlineStr">
         <is>
+          <t>80598 LEONCIO PRADO GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29060,6 +31336,16 @@
       </c>
       <c r="AD229" t="inlineStr">
         <is>
+          <t>SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29176,6 +31462,16 @@
       </c>
       <c r="AD230" t="inlineStr">
         <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29292,6 +31588,16 @@
       </c>
       <c r="AD231" t="inlineStr">
         <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29408,6 +31714,16 @@
       </c>
       <c r="AD232" t="inlineStr">
         <is>
+          <t>64525/64525/64525</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29524,6 +31840,16 @@
       </c>
       <c r="AD233" t="inlineStr">
         <is>
+          <t>QUILLISANI</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29640,6 +31966,16 @@
       </c>
       <c r="AD234" t="inlineStr">
         <is>
+          <t>597 VIRGEN DEL ROSARIO PALCA</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF234" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29756,6 +32092,16 @@
       </c>
       <c r="AD235" t="inlineStr">
         <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29876,6 +32222,16 @@
       </c>
       <c r="AD236" t="inlineStr">
         <is>
+          <t>50224</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -29992,6 +32348,16 @@
       </c>
       <c r="AD237" t="inlineStr">
         <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF237" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30108,6 +32474,16 @@
       </c>
       <c r="AD238" t="inlineStr">
         <is>
+          <t>501318</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF238" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30224,6 +32600,16 @@
       </c>
       <c r="AD239" t="inlineStr">
         <is>
+          <t>38396</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF239" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30346,6 +32732,16 @@
       </c>
       <c r="AD240" t="inlineStr">
         <is>
+          <t>38595</t>
+        </is>
+      </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF240" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30462,6 +32858,16 @@
       </c>
       <c r="AD241" t="inlineStr">
         <is>
+          <t>881 RAYITOS DE SOL</t>
+        </is>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF241" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30578,6 +32984,16 @@
       </c>
       <c r="AD242" t="inlineStr">
         <is>
+          <t>51043 VIRGEN DE CHAPI/51043 VIRGEN DE CHAPI</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30696,6 +33112,16 @@
       </c>
       <c r="AD243" t="inlineStr">
         <is>
+          <t>SANTA RITA DE SIGUAS</t>
+        </is>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF243" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30814,6 +33240,16 @@
       </c>
       <c r="AD244" t="inlineStr">
         <is>
+          <t>MARIANO MELGAR</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -30932,6 +33368,16 @@
       </c>
       <c r="AD245" t="inlineStr">
         <is>
+          <t>80051/80051</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31052,6 +33498,16 @@
       </c>
       <c r="AD246" t="inlineStr">
         <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31172,6 +33628,16 @@
       </c>
       <c r="AD247" t="inlineStr">
         <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31292,6 +33758,16 @@
       </c>
       <c r="AD248" t="inlineStr">
         <is>
+          <t>AMAQUILLA</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31412,6 +33888,16 @@
       </c>
       <c r="AD249" t="inlineStr">
         <is>
+          <t>14246</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31534,6 +34020,16 @@
       </c>
       <c r="AD250" t="inlineStr">
         <is>
+          <t>RAUL PORRAS BARRENECHEA</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31652,6 +34148,16 @@
       </c>
       <c r="AD251" t="inlineStr">
         <is>
+          <t>0371/0371</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31774,6 +34280,16 @@
       </c>
       <c r="AD252" t="inlineStr">
         <is>
+          <t>SOR ANA - B/SOR ANA - B</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -31890,6 +34406,16 @@
       </c>
       <c r="AD253" t="inlineStr">
         <is>
+          <t>16484/16484/16484</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32006,6 +34532,16 @@
       </c>
       <c r="AD254" t="inlineStr">
         <is>
+          <t>HORACIO ZEVALLOS GAMES</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32130,6 +34666,16 @@
       </c>
       <c r="AD255" t="inlineStr">
         <is>
+          <t>1057/821383</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32252,6 +34798,16 @@
       </c>
       <c r="AD256" t="inlineStr">
         <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32370,6 +34926,16 @@
       </c>
       <c r="AD257" t="inlineStr">
         <is>
+          <t>JOSE PARDO Y BARREDA/JOSE PARDO Y BARREDA/JOSE PARDO Y BARREDA</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF257" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32492,6 +35058,16 @@
       </c>
       <c r="AD258" t="inlineStr">
         <is>
+          <t>22443 JOSE GABRIEL AGUILAR/22443 JOSE GABRIEL AGUILAR/22443 JOSE GABRIEL AGUILAR</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF258" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32612,6 +35188,16 @@
       </c>
       <c r="AD259" t="inlineStr">
         <is>
+          <t>JOSE TORIBIO POLO</t>
+        </is>
+      </c>
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF259" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32736,6 +35322,16 @@
       </c>
       <c r="AD260" t="inlineStr">
         <is>
+          <t>SANTO DOMINGO/SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF260" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32858,6 +35454,16 @@
       </c>
       <c r="AD261" t="inlineStr">
         <is>
+          <t>52072 MARIO VARGAS LLOSA/52072 MARIO VARGAS LLOSA</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -32986,6 +35592,16 @@
       </c>
       <c r="AD262" t="inlineStr">
         <is>
+          <t>JUAN MANUEL MORE YOVERA/JUAN MANUEL MORE YOVERA</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF262" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33112,6 +35728,16 @@
       </c>
       <c r="AD263" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF263" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33238,6 +35864,16 @@
       </c>
       <c r="AD264" t="inlineStr">
         <is>
+          <t>30407 LA ASUNCION DE LA VIRGEN</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF264" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33366,6 +36002,16 @@
       </c>
       <c r="AD265" t="inlineStr">
         <is>
+          <t>CORONEL LEONCIO PRADO/CORONEL LEONCIO PRADO/CORONEL LEONCIO PRADO</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33490,6 +36136,16 @@
       </c>
       <c r="AD266" t="inlineStr">
         <is>
+          <t>413/32088</t>
+        </is>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF266" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33618,6 +36274,16 @@
       </c>
       <c r="AD267" t="inlineStr">
         <is>
+          <t>32678/32678</t>
+        </is>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF267" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33736,6 +36402,16 @@
       </c>
       <c r="AD268" t="inlineStr">
         <is>
+          <t>REYNO UNIDO</t>
+        </is>
+      </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF268" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33854,6 +36530,16 @@
       </c>
       <c r="AD269" t="inlineStr">
         <is>
+          <t>50161/50161</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -33976,6 +36662,16 @@
       </c>
       <c r="AD270" t="inlineStr">
         <is>
+          <t>81946 CESAR VALLEJO</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -34094,6 +36790,16 @@
       </c>
       <c r="AD271" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -34212,6 +36918,16 @@
       </c>
       <c r="AD272" t="inlineStr">
         <is>
+          <t>SEÑOR DE LOS MILAGROS/SEÑOR DE LOS MILAGROS/SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -34336,6 +37052,16 @@
       </c>
       <c r="AD273" t="inlineStr">
         <is>
+          <t>42096 MATEO PUMACAHUA</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -34458,6 +37184,16 @@
       </c>
       <c r="AD274" t="inlineStr">
         <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF274" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -34580,6 +37316,16 @@
       </c>
       <c r="AD275" t="inlineStr">
         <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF275" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -34702,6 +37448,16 @@
       </c>
       <c r="AD276" t="inlineStr">
         <is>
+          <t>TECNICO INDUSTRIAL NUÑOA</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF276" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -34822,6 +37578,16 @@
       </c>
       <c r="AD277" t="inlineStr">
         <is>
+          <t>32540</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF277" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -34946,6 +37712,16 @@
       </c>
       <c r="AD278" t="inlineStr">
         <is>
+          <t>82018/82018/82018</t>
+        </is>
+      </c>
+      <c r="AE278" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF278" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -35066,6 +37842,16 @@
       </c>
       <c r="AD279" t="inlineStr">
         <is>
+          <t>11156 LUIS ALBERTO GARCIA ROJAS/11156 LUIS ALBERTO GARCIA ROJAS</t>
+        </is>
+      </c>
+      <c r="AE279" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF279" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -35192,6 +37978,16 @@
       </c>
       <c r="AD280" t="inlineStr">
         <is>
+          <t>SAN JUAN</t>
+        </is>
+      </c>
+      <c r="AE280" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF280" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -35316,6 +38112,16 @@
       </c>
       <c r="AD281" t="inlineStr">
         <is>
+          <t>60029/60029</t>
+        </is>
+      </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF281" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -35434,6 +38240,16 @@
       </c>
       <c r="AD282" t="inlineStr">
         <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="AE282" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF282" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -35550,6 +38366,16 @@
       </c>
       <c r="AD283" t="inlineStr">
         <is>
+          <t>70497</t>
+        </is>
+      </c>
+      <c r="AE283" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF283" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -35666,6 +38492,16 @@
       </c>
       <c r="AD284" t="inlineStr">
         <is>
+          <t>54271</t>
+        </is>
+      </c>
+      <c r="AE284" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF284" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -35784,6 +38620,16 @@
       </c>
       <c r="AD285" t="inlineStr">
         <is>
+          <t>ANDRES AVELINO CACERES/ANDRES AVELINO CACERES</t>
+        </is>
+      </c>
+      <c r="AE285" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF285" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -35902,6 +38748,16 @@
       </c>
       <c r="AD286" t="inlineStr">
         <is>
+          <t>379 MUNDO MAGICO/379 MUNDO MAGICO</t>
+        </is>
+      </c>
+      <c r="AE286" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF286" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -36020,6 +38876,16 @@
       </c>
       <c r="AD287" t="inlineStr">
         <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="AE287" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF287" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -36138,6 +39004,16 @@
       </c>
       <c r="AD288" t="inlineStr">
         <is>
+          <t>VIRGEN DEL CARMEN/VIRGEN DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF288" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -36256,6 +39132,16 @@
       </c>
       <c r="AD289" t="inlineStr">
         <is>
+          <t>56127</t>
+        </is>
+      </c>
+      <c r="AE289" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF289" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -36374,6 +39260,16 @@
       </c>
       <c r="AD290" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AE290" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF290" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -36490,6 +39386,16 @@
       </c>
       <c r="AD291" t="inlineStr">
         <is>
+          <t>1337</t>
+        </is>
+      </c>
+      <c r="AE291" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF291" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -36608,6 +39514,16 @@
       </c>
       <c r="AD292" t="inlineStr">
         <is>
+          <t>80792/80792</t>
+        </is>
+      </c>
+      <c r="AE292" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF292" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -36726,6 +39642,16 @@
       </c>
       <c r="AD293" t="inlineStr">
         <is>
+          <t>70493</t>
+        </is>
+      </c>
+      <c r="AE293" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF293" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -36844,6 +39770,16 @@
       </c>
       <c r="AD294" t="inlineStr">
         <is>
+          <t>AGROPECUARIO DE PUERTO SUNGARO</t>
+        </is>
+      </c>
+      <c r="AE294" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF294" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -36962,6 +39898,16 @@
       </c>
       <c r="AD295" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AE295" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF295" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -37080,6 +40026,16 @@
       </c>
       <c r="AD296" t="inlineStr">
         <is>
+          <t>80337/80337/80337</t>
+        </is>
+      </c>
+      <c r="AE296" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF296" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -37198,6 +40154,16 @@
       </c>
       <c r="AD297" t="inlineStr">
         <is>
+          <t>JORGE BASADRE/JORGE BASADRE</t>
+        </is>
+      </c>
+      <c r="AE297" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF297" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -37316,6 +40282,16 @@
       </c>
       <c r="AD298" t="inlineStr">
         <is>
+          <t>1191/501314</t>
+        </is>
+      </c>
+      <c r="AE298" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF298" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -37434,6 +40410,16 @@
       </c>
       <c r="AD299" t="inlineStr">
         <is>
+          <t>62461 SANTO TOMAS/62461 SANTO TOMAS/62461 SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="AE299" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF299" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -37552,6 +40538,16 @@
       </c>
       <c r="AD300" t="inlineStr">
         <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="AE300" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF300" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -37670,6 +40666,16 @@
       </c>
       <c r="AD301" t="inlineStr">
         <is>
+          <t>16624 DEFENSORES DEL SANTUARIO/16624 DEFENSORES DEL SANTUARIO</t>
+        </is>
+      </c>
+      <c r="AE301" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF301" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -37788,6 +40794,16 @@
       </c>
       <c r="AD302" t="inlineStr">
         <is>
+          <t>JOSE MACEDO MENDOZA</t>
+        </is>
+      </c>
+      <c r="AE302" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF302" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -37906,6 +40922,16 @@
       </c>
       <c r="AD303" t="inlineStr">
         <is>
+          <t>40156 NUESTRA SEÑORA DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="AE303" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF303" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -38022,6 +41048,16 @@
       </c>
       <c r="AD304" t="inlineStr">
         <is>
+          <t>SAN FRANCISCO</t>
+        </is>
+      </c>
+      <c r="AE304" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF304" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -38138,6 +41174,16 @@
       </c>
       <c r="AD305" t="inlineStr">
         <is>
+          <t>FLORENCIA DE MORA</t>
+        </is>
+      </c>
+      <c r="AE305" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF305" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -38254,6 +41300,16 @@
       </c>
       <c r="AD306" t="inlineStr">
         <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="AE306" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF306" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -38370,6 +41426,16 @@
       </c>
       <c r="AD307" t="inlineStr">
         <is>
+          <t>JOSE MARIA MONZON HERNANDEZ/JOSE MARIA MONZON HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="AE307" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF307" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -38486,6 +41552,16 @@
       </c>
       <c r="AD308" t="inlineStr">
         <is>
+          <t>479/16148/16148</t>
+        </is>
+      </c>
+      <c r="AE308" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF308" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -38602,6 +41678,16 @@
       </c>
       <c r="AD309" t="inlineStr">
         <is>
+          <t>NUESTRO SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="AE309" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF309" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -38718,6 +41804,16 @@
       </c>
       <c r="AD310" t="inlineStr">
         <is>
+          <t>54258 JUAN ESPINOZA MEDRANO</t>
+        </is>
+      </c>
+      <c r="AE310" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF310" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -38834,6 +41930,16 @@
       </c>
       <c r="AD311" t="inlineStr">
         <is>
+          <t>025</t>
+        </is>
+      </c>
+      <c r="AE311" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF311" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -38950,6 +42056,16 @@
       </c>
       <c r="AD312" t="inlineStr">
         <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="AE312" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF312" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -39066,6 +42182,16 @@
       </c>
       <c r="AD313" t="inlineStr">
         <is>
+          <t>15396/15396/15396</t>
+        </is>
+      </c>
+      <c r="AE313" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF313" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -39182,6 +42308,16 @@
       </c>
       <c r="AD314" t="inlineStr">
         <is>
+          <t>994</t>
+        </is>
+      </c>
+      <c r="AE314" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF314" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -39298,6 +42434,16 @@
       </c>
       <c r="AD315" t="inlineStr">
         <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="AE315" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF315" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -39414,6 +42560,16 @@
       </c>
       <c r="AD316" t="inlineStr">
         <is>
+          <t>048</t>
+        </is>
+      </c>
+      <c r="AE316" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF316" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -39536,6 +42692,16 @@
       </c>
       <c r="AD317" t="inlineStr">
         <is>
+          <t>420 FANNY ABANTO CALLE</t>
+        </is>
+      </c>
+      <c r="AE317" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF317" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -39652,6 +42818,16 @@
       </c>
       <c r="AD318" t="inlineStr">
         <is>
+          <t>PNP (R) NAVIO COMUN GAVILAN</t>
+        </is>
+      </c>
+      <c r="AE318" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF318" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -39772,6 +42948,16 @@
       </c>
       <c r="AD319" t="inlineStr">
         <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="AE319" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF319" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -39886,6 +43072,16 @@
       </c>
       <c r="AD320" t="inlineStr">
         <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AE320" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF320" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -40006,6 +43202,16 @@
       </c>
       <c r="AD321" t="inlineStr">
         <is>
+          <t>440 ANGELITOS DE MARIA</t>
+        </is>
+      </c>
+      <c r="AE321" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF321" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -40126,6 +43332,16 @@
       </c>
       <c r="AD322" t="inlineStr">
         <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="AE322" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF322" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -40246,6 +43462,16 @@
       </c>
       <c r="AD323" t="inlineStr">
         <is>
+          <t>1528</t>
+        </is>
+      </c>
+      <c r="AE323" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF323" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -40368,6 +43594,16 @@
       </c>
       <c r="AD324" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AE324" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF324" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -40490,6 +43726,16 @@
       </c>
       <c r="AD325" t="inlineStr">
         <is>
+          <t>64440</t>
+        </is>
+      </c>
+      <c r="AE325" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF325" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -40614,6 +43860,16 @@
       </c>
       <c r="AD326" t="inlineStr">
         <is>
+          <t>LUIS PAREDES MACEDA/LUIS PAREDES MACEDA/LUIS PAREDES MACEDA</t>
+        </is>
+      </c>
+      <c r="AE326" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF326" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -40732,6 +43988,16 @@
       </c>
       <c r="AD327" t="inlineStr">
         <is>
+          <t>15116</t>
+        </is>
+      </c>
+      <c r="AE327" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF327" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -40848,6 +44114,16 @@
       </c>
       <c r="AD328" t="inlineStr">
         <is>
+          <t>33266</t>
+        </is>
+      </c>
+      <c r="AE328" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF328" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -40966,6 +44242,16 @@
       </c>
       <c r="AD329" t="inlineStr">
         <is>
+          <t>38309</t>
+        </is>
+      </c>
+      <c r="AE329" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AF329" t="inlineStr">
+        <is>
           <t>UGSC</t>
         </is>
       </c>
@@ -41083,6 +44369,16 @@
         </is>
       </c>
       <c r="AD330" t="inlineStr">
+        <is>
+          <t>60092 PADRE MEDARDO ANDRE</t>
+        </is>
+      </c>
+      <c r="AE330" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AF330" t="inlineStr">
         <is>
           <t>UGSC</t>
         </is>
@@ -41124,7 +44420,9 @@
       <c r="AA331" t="inlineStr"/>
       <c r="AB331" t="inlineStr"/>
       <c r="AC331" t="inlineStr"/>
-      <c r="AD331" t="inlineStr">
+      <c r="AD331" t="inlineStr"/>
+      <c r="AE331" t="inlineStr"/>
+      <c r="AF331" t="inlineStr">
         <is>
           <t>UGSC</t>
         </is>

--- a/output/bases_limpias/Grupo_10_INSPECCIONES/df_ugsc_seguimiento.xlsx
+++ b/output/bases_limpias/Grupo_10_INSPECCIONES/df_ugsc_seguimiento.xlsx
@@ -3441,7 +3441,11 @@
           <t>0600 AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
       <c r="AF22" t="inlineStr">
         <is>
           <t>UGSC</t>

--- a/output/bases_limpias/Grupo_10_INSPECCIONES/df_ugsc_seguimiento.xlsx
+++ b/output/bases_limpias/Grupo_10_INSPECCIONES/df_ugsc_seguimiento.xlsx
@@ -419,27 +419,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>CUI</t>
+          <t>cui</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Año de la primera transferencia</t>
+          <t>ano_de_la_primera_transferencia</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Año de la última transferencia</t>
+          <t>ano_de_la_ultima_transferencia</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Documento de la transferencia (agregar columnas si las transferencias es mayor a 1 año)</t>
+          <t>documento_de_la_transferencia_agregar_columnas_si_las_transf</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -449,77 +449,77 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>nan (1)</t>
+          <t>nan_1</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>nan (2)</t>
+          <t>nan_2</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>nan (3)</t>
+          <t>nan_3</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>nan (4)</t>
+          <t>nan_4</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>nan (5)</t>
+          <t>nan_5</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>nan (6)</t>
+          <t>nan_6</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>nan (7)</t>
+          <t>nan_7</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>nan (8)</t>
+          <t>nan_8</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>nan (9)</t>
+          <t>nan_9</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>nan (10)</t>
+          <t>nan_10</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Estado del proyecto de inversión (PI) (en ejecución de obra, transferencia de obra, obra en proceso de selección, contratación de obra, incorporación de recursos, ET apto para financiamiento, liquidación de obra, recepción de obra, contrato resuelto, culminación de obra, suspendida, ET aprobado, paralizado, cerrado, convenio resuelto, ET en elaboración, adjudicación de obra, etc.)</t>
+          <t>estado_del_proyecto_de_inversion_pi_en_ejecucion_de_obra_tra</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Cantidad de locales educativos intervenidos por el PI</t>
+          <t>cantidad_de_locales_educativos_intervenidos_por_el_pi</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Monto de Inversión (S/)</t>
+          <t>monto</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Transferencia total (S/)</t>
+          <t>transferencia_total_s</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Comentarios</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
